--- a/research/traditional_assets/database/data/south_africa/south_africa_furn_home_furnishings.xlsx
+++ b/research/traditional_assets/database/data/south_africa/south_africa_furn_home_furnishings.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1238041405174709</v>
+        <v>0.1235027193380737</v>
       </c>
       <c r="C2">
-        <v>32.11103478587558</v>
+        <v>31.79890306973407</v>
       </c>
       <c r="D2">
-        <v>6.711034785875586</v>
+        <v>6.720103069734073</v>
       </c>
       <c r="E2">
-        <v>-2.02</v>
+        <v>-1.6988</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.3212</v>
       </c>
       <c r="G2">
         <v>25.4</v>
@@ -1451,28 +1451,28 @@
         <v>2.46</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.01615636</v>
       </c>
       <c r="N2">
-        <v>2.46</v>
+        <v>2.44384364</v>
       </c>
       <c r="O2">
-        <v>0.6642</v>
+        <v>0.6598377828000001</v>
       </c>
       <c r="P2">
-        <v>1.7958</v>
+        <v>1.7840058572</v>
       </c>
       <c r="Q2">
-        <v>1.9358</v>
+        <v>1.9240058572</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1238041405174709</v>
+        <v>0.1243793225637108</v>
       </c>
       <c r="T2">
-        <v>0.9344695036460947</v>
+        <v>0.9413600363497479</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>152.2620194152643</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1235027193380737</v>
+        <v>0.1232012981586766</v>
       </c>
       <c r="C3">
-        <v>31.79890306973407</v>
+        <v>31.48679589378449</v>
       </c>
       <c r="D3">
-        <v>6.720103069734073</v>
+        <v>6.729195893784492</v>
       </c>
       <c r="E3">
-        <v>-1.6988</v>
+        <v>-1.3776</v>
       </c>
       <c r="F3">
-        <v>0.3212</v>
+        <v>0.6424000000000001</v>
       </c>
       <c r="G3">
         <v>25.4</v>
@@ -1533,28 +1533,28 @@
         <v>2.46</v>
       </c>
       <c r="M3">
-        <v>0.01615636</v>
+        <v>0.03231272</v>
       </c>
       <c r="N3">
-        <v>2.44384364</v>
+        <v>2.42768728</v>
       </c>
       <c r="O3">
-        <v>0.6598377828000001</v>
+        <v>0.6554755656</v>
       </c>
       <c r="P3">
-        <v>1.7840058572</v>
+        <v>1.7722117144</v>
       </c>
       <c r="Q3">
-        <v>1.9240058572</v>
+        <v>1.9122117144</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1243793225637108</v>
+        <v>0.1249662430190577</v>
       </c>
       <c r="T3">
-        <v>0.9413600363497479</v>
+        <v>0.9483911921698019</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>152.2620194152643</v>
+        <v>76.13100970763215</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1232012981586766</v>
+        <v>0.1228998769792794</v>
       </c>
       <c r="C4">
-        <v>31.48679589378449</v>
+        <v>31.1747133577762</v>
       </c>
       <c r="D4">
-        <v>6.729195893784492</v>
+        <v>6.738313357776198</v>
       </c>
       <c r="E4">
-        <v>-1.3776</v>
+        <v>-1.0564</v>
       </c>
       <c r="F4">
-        <v>0.6424000000000001</v>
+        <v>0.9636000000000001</v>
       </c>
       <c r="G4">
         <v>25.4</v>
@@ -1615,28 +1615,28 @@
         <v>2.46</v>
       </c>
       <c r="M4">
-        <v>0.03231272</v>
+        <v>0.04846908</v>
       </c>
       <c r="N4">
-        <v>2.42768728</v>
+        <v>2.41153092</v>
       </c>
       <c r="O4">
-        <v>0.6554755656</v>
+        <v>0.6511133484000001</v>
       </c>
       <c r="P4">
-        <v>1.7722117144</v>
+        <v>1.7604175716</v>
       </c>
       <c r="Q4">
-        <v>1.9122117144</v>
+        <v>1.9004175716</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1249662430190577</v>
+        <v>0.1255652649270921</v>
       </c>
       <c r="T4">
-        <v>0.9483911921698019</v>
+        <v>0.9555673202748055</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>76.13100970763215</v>
+        <v>50.75400647175478</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1228998769792794</v>
+        <v>0.1225984557998822</v>
       </c>
       <c r="C5">
-        <v>31.1747133577762</v>
+        <v>30.86265556199988</v>
       </c>
       <c r="D5">
-        <v>6.738313357776198</v>
+        <v>6.747455561999882</v>
       </c>
       <c r="E5">
-        <v>-1.0564</v>
+        <v>-0.7351999999999999</v>
       </c>
       <c r="F5">
-        <v>0.9636000000000001</v>
+        <v>1.2848</v>
       </c>
       <c r="G5">
         <v>25.4</v>
@@ -1697,28 +1697,28 @@
         <v>2.46</v>
       </c>
       <c r="M5">
-        <v>0.04846908</v>
+        <v>0.06462544000000001</v>
       </c>
       <c r="N5">
-        <v>2.41153092</v>
+        <v>2.39537456</v>
       </c>
       <c r="O5">
-        <v>0.6511133484000001</v>
+        <v>0.6467511312000001</v>
       </c>
       <c r="P5">
-        <v>1.7604175716</v>
+        <v>1.7486234288</v>
       </c>
       <c r="Q5">
-        <v>1.9004175716</v>
+        <v>1.8886234288</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1255652649270921</v>
+        <v>0.1261767664582106</v>
       </c>
       <c r="T5">
-        <v>0.9555673202748055</v>
+        <v>0.9628929510486635</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>50.75400647175478</v>
+        <v>38.06550485381608</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1225984557998822</v>
+        <v>0.122297034620485</v>
       </c>
       <c r="C6">
-        <v>30.86265556199988</v>
+        <v>30.55062260729125</v>
       </c>
       <c r="D6">
-        <v>6.747455561999882</v>
+        <v>6.756622607291259</v>
       </c>
       <c r="E6">
-        <v>-0.7351999999999999</v>
+        <v>-0.4139999999999997</v>
       </c>
       <c r="F6">
-        <v>1.2848</v>
+        <v>1.606</v>
       </c>
       <c r="G6">
         <v>25.4</v>
@@ -1779,28 +1779,28 @@
         <v>2.46</v>
       </c>
       <c r="M6">
-        <v>0.06462544000000001</v>
+        <v>0.08078180000000001</v>
       </c>
       <c r="N6">
-        <v>2.39537456</v>
+        <v>2.3792182</v>
       </c>
       <c r="O6">
-        <v>0.6467511312000001</v>
+        <v>0.642388914</v>
       </c>
       <c r="P6">
-        <v>1.7486234288</v>
+        <v>1.736829286</v>
       </c>
       <c r="Q6">
-        <v>1.8886234288</v>
+        <v>1.876829286</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1261767664582106</v>
+        <v>0.1268011417057737</v>
       </c>
       <c r="T6">
-        <v>0.9628929510486635</v>
+        <v>0.9703728056282868</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>38.06550485381608</v>
+        <v>30.45240388305286</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.122297034620485</v>
+        <v>0.1219956134410878</v>
       </c>
       <c r="C7">
-        <v>30.55062260729125</v>
+        <v>30.23861459503476</v>
       </c>
       <c r="D7">
-        <v>6.756622607291259</v>
+        <v>6.765814595034764</v>
       </c>
       <c r="E7">
-        <v>-0.4139999999999997</v>
+        <v>-0.09279999999999955</v>
       </c>
       <c r="F7">
-        <v>1.606</v>
+        <v>1.9272</v>
       </c>
       <c r="G7">
         <v>25.4</v>
@@ -1861,28 +1861,28 @@
         <v>2.46</v>
       </c>
       <c r="M7">
-        <v>0.08078180000000001</v>
+        <v>0.09693816000000002</v>
       </c>
       <c r="N7">
-        <v>2.3792182</v>
+        <v>2.36306184</v>
       </c>
       <c r="O7">
-        <v>0.642388914</v>
+        <v>0.6380266968</v>
       </c>
       <c r="P7">
-        <v>1.736829286</v>
+        <v>1.7250351432</v>
       </c>
       <c r="Q7">
-        <v>1.876829286</v>
+        <v>1.8650351432</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1268011417057737</v>
+        <v>0.1274388015330722</v>
       </c>
       <c r="T7">
-        <v>0.9703728056282868</v>
+        <v>0.9780118060500298</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>30.45240388305286</v>
+        <v>25.37700323587738</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1219956134410878</v>
+        <v>0.1216941922616907</v>
       </c>
       <c r="C8">
-        <v>30.23861459503476</v>
+        <v>29.92663162716729</v>
       </c>
       <c r="D8">
-        <v>6.765814595034764</v>
+        <v>6.775031627167293</v>
       </c>
       <c r="E8">
-        <v>-0.09279999999999977</v>
+        <v>0.2284000000000002</v>
       </c>
       <c r="F8">
-        <v>1.9272</v>
+        <v>2.2484</v>
       </c>
       <c r="G8">
         <v>25.4</v>
@@ -1943,28 +1943,28 @@
         <v>2.46</v>
       </c>
       <c r="M8">
-        <v>0.09693816000000001</v>
+        <v>0.11309452</v>
       </c>
       <c r="N8">
-        <v>2.36306184</v>
+        <v>2.34690548</v>
       </c>
       <c r="O8">
-        <v>0.6380266968</v>
+        <v>0.6336644795999999</v>
       </c>
       <c r="P8">
-        <v>1.7250351432</v>
+        <v>1.7132410004</v>
       </c>
       <c r="Q8">
-        <v>1.8650351432</v>
+        <v>1.8532410004</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1274388015330722</v>
+        <v>0.1280901744749362</v>
       </c>
       <c r="T8">
-        <v>0.9780118060500298</v>
+        <v>0.985815086050735</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>25.37700323587739</v>
+        <v>21.75171705932347</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1216941922616907</v>
+        <v>0.1213927710822935</v>
       </c>
       <c r="C9">
-        <v>29.92663162716729</v>
+        <v>29.61467380618197</v>
       </c>
       <c r="D9">
-        <v>6.775031627167294</v>
+        <v>6.784273806181974</v>
       </c>
       <c r="E9">
-        <v>0.2284000000000006</v>
+        <v>0.5496000000000003</v>
       </c>
       <c r="F9">
-        <v>2.248400000000001</v>
+        <v>2.5696</v>
       </c>
       <c r="G9">
         <v>25.4</v>
@@ -2025,28 +2025,28 @@
         <v>2.46</v>
       </c>
       <c r="M9">
-        <v>0.11309452</v>
+        <v>0.12925088</v>
       </c>
       <c r="N9">
-        <v>2.34690548</v>
+        <v>2.33074912</v>
       </c>
       <c r="O9">
-        <v>0.6336644795999999</v>
+        <v>0.6293022624000001</v>
       </c>
       <c r="P9">
-        <v>1.7132410004</v>
+        <v>1.7014468576</v>
       </c>
       <c r="Q9">
-        <v>1.8532410004</v>
+        <v>1.8414468576</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1280901744749362</v>
+        <v>0.1287557076981451</v>
       </c>
       <c r="T9">
-        <v>0.985815086050735</v>
+        <v>0.9937880025731947</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>21.75171705932347</v>
+        <v>19.03275242690804</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1213927710822935</v>
+        <v>0.1210913499028964</v>
       </c>
       <c r="C10">
-        <v>29.61467380618197</v>
+        <v>29.30274123513196</v>
       </c>
       <c r="D10">
-        <v>6.784273806181974</v>
+        <v>6.793541235131965</v>
       </c>
       <c r="E10">
-        <v>0.5496000000000003</v>
+        <v>0.8708000000000005</v>
       </c>
       <c r="F10">
-        <v>2.5696</v>
+        <v>2.8908</v>
       </c>
       <c r="G10">
         <v>25.4</v>
@@ -2107,28 +2107,28 @@
         <v>2.46</v>
       </c>
       <c r="M10">
-        <v>0.12925088</v>
+        <v>0.14540724</v>
       </c>
       <c r="N10">
-        <v>2.33074912</v>
+        <v>2.31459276</v>
       </c>
       <c r="O10">
-        <v>0.6293022624000001</v>
+        <v>0.6249400452</v>
       </c>
       <c r="P10">
-        <v>1.7014468576</v>
+        <v>1.6896527148</v>
       </c>
       <c r="Q10">
-        <v>1.8414468576</v>
+        <v>1.8296527148</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1287557076981451</v>
+        <v>0.1294358680251608</v>
       </c>
       <c r="T10">
-        <v>0.9937880025731947</v>
+        <v>1.001936148030214</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>19.03275242690804</v>
+        <v>16.91800215725159</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1210913499028964</v>
+        <v>0.1207899287234992</v>
       </c>
       <c r="C11">
-        <v>29.30274123513196</v>
+        <v>28.99083401763427</v>
       </c>
       <c r="D11">
-        <v>6.793541235131965</v>
+        <v>6.802834017634279</v>
       </c>
       <c r="E11">
-        <v>0.8708000000000005</v>
+        <v>1.192</v>
       </c>
       <c r="F11">
-        <v>2.8908</v>
+        <v>3.212</v>
       </c>
       <c r="G11">
         <v>25.4</v>
@@ -2189,28 +2189,28 @@
         <v>2.46</v>
       </c>
       <c r="M11">
-        <v>0.14540724</v>
+        <v>0.1615636</v>
       </c>
       <c r="N11">
-        <v>2.31459276</v>
+        <v>2.2984364</v>
       </c>
       <c r="O11">
-        <v>0.6249400452</v>
+        <v>0.6205778280000001</v>
       </c>
       <c r="P11">
-        <v>1.6896527148</v>
+        <v>1.677858572</v>
       </c>
       <c r="Q11">
-        <v>1.8296527148</v>
+        <v>1.817858572</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1294358680251608</v>
+        <v>0.1301311430261102</v>
       </c>
       <c r="T11">
-        <v>1.001936148030214</v>
+        <v>1.010265363386278</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.91800215725159</v>
+        <v>15.22620194152643</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1207899287234992</v>
+        <v>0.120488507544102</v>
       </c>
       <c r="C12">
-        <v>28.99083401763427</v>
+        <v>28.67895225787365</v>
       </c>
       <c r="D12">
-        <v>6.802834017634279</v>
+        <v>6.812152257873656</v>
       </c>
       <c r="E12">
-        <v>1.192000000000001</v>
+        <v>1.5132</v>
       </c>
       <c r="F12">
-        <v>3.212000000000001</v>
+        <v>3.5332</v>
       </c>
       <c r="G12">
         <v>25.4</v>
@@ -2271,28 +2271,28 @@
         <v>2.46</v>
       </c>
       <c r="M12">
-        <v>0.1615636</v>
+        <v>0.17771996</v>
       </c>
       <c r="N12">
-        <v>2.2984364</v>
+        <v>2.28228004</v>
       </c>
       <c r="O12">
-        <v>0.6205778280000001</v>
+        <v>0.6162156108</v>
       </c>
       <c r="P12">
-        <v>1.677858572</v>
+        <v>1.6660644292</v>
       </c>
       <c r="Q12">
-        <v>1.817858572</v>
+        <v>1.8060644292</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1301311430261102</v>
+        <v>0.1308420421843843</v>
       </c>
       <c r="T12">
-        <v>1.010265363386278</v>
+        <v>1.01878175212113</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>15.22620194152643</v>
+        <v>13.84200176502403</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.120488507544102</v>
+        <v>0.1203184863647048</v>
       </c>
       <c r="C13">
-        <v>28.67895225787365</v>
+        <v>28.36301962166765</v>
       </c>
       <c r="D13">
-        <v>6.812152257873656</v>
+        <v>6.817419621667652</v>
       </c>
       <c r="E13">
-        <v>1.5132</v>
+        <v>1.8344</v>
       </c>
       <c r="F13">
-        <v>3.5332</v>
+        <v>3.8544</v>
       </c>
       <c r="G13">
         <v>25.4</v>
@@ -2353,45 +2353,45 @@
         <v>2.46</v>
       </c>
       <c r="M13">
-        <v>0.17771996</v>
+        <v>0.19965792</v>
       </c>
       <c r="N13">
-        <v>2.28228004</v>
+        <v>2.26034208</v>
       </c>
       <c r="O13">
-        <v>0.6162156108</v>
+        <v>0.6102923616</v>
       </c>
       <c r="P13">
-        <v>1.6660644292</v>
+        <v>1.6500497184</v>
       </c>
       <c r="Q13">
-        <v>1.8060644292</v>
+        <v>1.7900497184</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1308420421843843</v>
+        <v>0.13156909814171</v>
       </c>
       <c r="T13">
-        <v>1.01878175212113</v>
+        <v>1.02749169514541</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.27</v>
       </c>
       <c r="W13">
-        <v>0.03671899999999999</v>
+        <v>0.037814</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>13.84200176502403</v>
+        <v>12.32107396490958</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1203184863647048</v>
+        <v>0.1200280151853077</v>
       </c>
       <c r="C14">
-        <v>28.36301962166765</v>
+        <v>28.05083747376824</v>
       </c>
       <c r="D14">
-        <v>6.817419621667652</v>
+        <v>6.826437473768246</v>
       </c>
       <c r="E14">
-        <v>1.8344</v>
+        <v>2.155600000000001</v>
       </c>
       <c r="F14">
-        <v>3.8544</v>
+        <v>4.175600000000001</v>
       </c>
       <c r="G14">
         <v>25.4</v>
@@ -2435,28 +2435,28 @@
         <v>2.46</v>
       </c>
       <c r="M14">
-        <v>0.19965792</v>
+        <v>0.2162960800000001</v>
       </c>
       <c r="N14">
-        <v>2.26034208</v>
+        <v>2.24370392</v>
       </c>
       <c r="O14">
-        <v>0.6102923616</v>
+        <v>0.6058000584</v>
       </c>
       <c r="P14">
-        <v>1.6500497184</v>
+        <v>1.6379038616</v>
       </c>
       <c r="Q14">
-        <v>1.7900497184</v>
+        <v>1.7779038616</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.13156909814171</v>
+        <v>0.1323128680290893</v>
       </c>
       <c r="T14">
-        <v>1.02749169514541</v>
+        <v>1.036401866744962</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>12.32107396490958</v>
+        <v>11.37329904453192</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1200280151853077</v>
+        <v>0.1197375440059105</v>
       </c>
       <c r="C15">
-        <v>28.05083747376824</v>
+        <v>27.73867921448742</v>
       </c>
       <c r="D15">
-        <v>6.826437473768246</v>
+        <v>6.83547921448742</v>
       </c>
       <c r="E15">
-        <v>2.155600000000001</v>
+        <v>2.476800000000001</v>
       </c>
       <c r="F15">
-        <v>4.175600000000001</v>
+        <v>4.496800000000001</v>
       </c>
       <c r="G15">
         <v>25.4</v>
@@ -2517,28 +2517,28 @@
         <v>2.46</v>
       </c>
       <c r="M15">
-        <v>0.2162960800000001</v>
+        <v>0.2329342400000001</v>
       </c>
       <c r="N15">
-        <v>2.24370392</v>
+        <v>2.22706576</v>
       </c>
       <c r="O15">
-        <v>0.6058000584</v>
+        <v>0.6013077552</v>
       </c>
       <c r="P15">
-        <v>1.6379038616</v>
+        <v>1.6257580048</v>
       </c>
       <c r="Q15">
-        <v>1.7779038616</v>
+        <v>1.7657580048</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1323128680290893</v>
+        <v>0.1330739348905936</v>
       </c>
       <c r="T15">
-        <v>1.036401866744962</v>
+        <v>1.045519251637526</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.37329904453192</v>
+        <v>10.56092054135107</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1197375440059105</v>
+        <v>0.1194470728265133</v>
       </c>
       <c r="C16">
-        <v>27.73867921448742</v>
+        <v>27.4265449388738</v>
       </c>
       <c r="D16">
-        <v>6.83547921448742</v>
+        <v>6.844544938873802</v>
       </c>
       <c r="E16">
-        <v>2.476800000000001</v>
+        <v>2.798000000000001</v>
       </c>
       <c r="F16">
-        <v>4.496800000000001</v>
+        <v>4.818000000000001</v>
       </c>
       <c r="G16">
         <v>25.4</v>
@@ -2599,28 +2599,28 @@
         <v>2.46</v>
       </c>
       <c r="M16">
-        <v>0.2329342400000001</v>
+        <v>0.2495724000000001</v>
       </c>
       <c r="N16">
-        <v>2.22706576</v>
+        <v>2.2104276</v>
       </c>
       <c r="O16">
-        <v>0.6013077552</v>
+        <v>0.5968154520000001</v>
       </c>
       <c r="P16">
-        <v>1.6257580048</v>
+        <v>1.613612148</v>
       </c>
       <c r="Q16">
-        <v>1.7657580048</v>
+        <v>1.753612148</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1330739348905936</v>
+        <v>0.1338529092076627</v>
       </c>
       <c r="T16">
-        <v>1.045519251637526</v>
+        <v>1.054851163233445</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>10.56092054135107</v>
+        <v>9.856859171927663</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1194470728265133</v>
+        <v>0.1193551616471161</v>
       </c>
       <c r="C17">
-        <v>27.4265449388738</v>
+        <v>27.1082185348678</v>
       </c>
       <c r="D17">
-        <v>6.844544938873802</v>
+        <v>6.847418534867808</v>
       </c>
       <c r="E17">
-        <v>2.798</v>
+        <v>3.119200000000001</v>
       </c>
       <c r="F17">
-        <v>4.818000000000001</v>
+        <v>5.139200000000001</v>
       </c>
       <c r="G17">
         <v>25.4</v>
@@ -2681,45 +2681,45 @@
         <v>2.46</v>
       </c>
       <c r="M17">
-        <v>0.2495724</v>
+        <v>0.2749472</v>
       </c>
       <c r="N17">
-        <v>2.2104276</v>
+        <v>2.1850528</v>
       </c>
       <c r="O17">
-        <v>0.5968154520000001</v>
+        <v>0.589964256</v>
       </c>
       <c r="P17">
-        <v>1.613612148</v>
+        <v>1.595088544</v>
       </c>
       <c r="Q17">
-        <v>1.753612148</v>
+        <v>1.735088544</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1338529092076627</v>
+        <v>0.1346504305322811</v>
       </c>
       <c r="T17">
-        <v>1.054851163233445</v>
+        <v>1.064405263200695</v>
       </c>
       <c r="U17">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V17">
         <v>0.27</v>
       </c>
       <c r="W17">
-        <v>0.037814</v>
+        <v>0.039055</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>9.856859171927665</v>
+        <v>8.947172402555836</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1193551616471161</v>
+        <v>0.119077100467719</v>
       </c>
       <c r="C18">
-        <v>27.1082185348678</v>
+        <v>26.79572680702089</v>
       </c>
       <c r="D18">
-        <v>6.847418534867808</v>
+        <v>6.856126807020892</v>
       </c>
       <c r="E18">
-        <v>3.119200000000001</v>
+        <v>3.440400000000001</v>
       </c>
       <c r="F18">
-        <v>5.139200000000001</v>
+        <v>5.460400000000001</v>
       </c>
       <c r="G18">
         <v>25.4</v>
@@ -2763,28 +2763,28 @@
         <v>2.46</v>
       </c>
       <c r="M18">
-        <v>0.2749472</v>
+        <v>0.2921314</v>
       </c>
       <c r="N18">
-        <v>2.1850528</v>
+        <v>2.1678686</v>
       </c>
       <c r="O18">
-        <v>0.589964256</v>
+        <v>0.585324522</v>
       </c>
       <c r="P18">
-        <v>1.595088544</v>
+        <v>1.582544078</v>
       </c>
       <c r="Q18">
-        <v>1.735088544</v>
+        <v>1.722544078</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1346504305322811</v>
+        <v>0.1354671692382156</v>
       </c>
       <c r="T18">
-        <v>1.064405263200695</v>
+        <v>1.074189582444264</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.947172402555836</v>
+        <v>8.420868143581963</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.119077100467719</v>
+        <v>0.1187990392883218</v>
       </c>
       <c r="C19">
-        <v>26.79572680702089</v>
+        <v>26.48325725704114</v>
       </c>
       <c r="D19">
-        <v>6.856126807020892</v>
+        <v>6.864857257041142</v>
       </c>
       <c r="E19">
-        <v>3.440400000000001</v>
+        <v>3.761600000000002</v>
       </c>
       <c r="F19">
-        <v>5.460400000000001</v>
+        <v>5.781600000000002</v>
       </c>
       <c r="G19">
         <v>25.4</v>
@@ -2845,28 +2845,28 @@
         <v>2.46</v>
       </c>
       <c r="M19">
-        <v>0.2921314</v>
+        <v>0.3093156000000001</v>
       </c>
       <c r="N19">
-        <v>2.1678686</v>
+        <v>2.1506844</v>
       </c>
       <c r="O19">
-        <v>0.585324522</v>
+        <v>0.580684788</v>
       </c>
       <c r="P19">
-        <v>1.582544078</v>
+        <v>1.569999612</v>
       </c>
       <c r="Q19">
-        <v>1.722544078</v>
+        <v>1.709999612</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1354671692382156</v>
+        <v>0.1363038284003924</v>
       </c>
       <c r="T19">
-        <v>1.074189582444264</v>
+        <v>1.084212543620603</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.420868143581963</v>
+        <v>7.953042135605186</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1187990392883218</v>
+        <v>0.1186319381089247</v>
       </c>
       <c r="C20">
-        <v>26.48325725704114</v>
+        <v>26.16731453477936</v>
       </c>
       <c r="D20">
-        <v>6.864857257041142</v>
+        <v>6.87011453477936</v>
       </c>
       <c r="E20">
-        <v>3.761600000000001</v>
+        <v>4.082800000000001</v>
       </c>
       <c r="F20">
-        <v>5.781600000000001</v>
+        <v>6.102800000000001</v>
       </c>
       <c r="G20">
         <v>25.4</v>
@@ -2927,45 +2927,45 @@
         <v>2.46</v>
       </c>
       <c r="M20">
-        <v>0.3093156</v>
+        <v>0.33138204</v>
       </c>
       <c r="N20">
-        <v>2.1506844</v>
+        <v>2.12861796</v>
       </c>
       <c r="O20">
-        <v>0.580684788</v>
+        <v>0.5747268491999999</v>
       </c>
       <c r="P20">
-        <v>1.569999612</v>
+        <v>1.5538911108</v>
       </c>
       <c r="Q20">
-        <v>1.709999612</v>
+        <v>1.6938911108</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1363038284003924</v>
+        <v>0.1371611458134872</v>
       </c>
       <c r="T20">
-        <v>1.084212543620603</v>
+        <v>1.094482985319815</v>
       </c>
       <c r="U20">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V20">
         <v>0.27</v>
       </c>
       <c r="W20">
-        <v>0.039055</v>
+        <v>0.039639</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y20">
-        <v>7.953042135605187</v>
+        <v>7.423456020730633</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1186319381089247</v>
+        <v>0.1183597169295275</v>
       </c>
       <c r="C21">
-        <v>26.16731453477936</v>
+        <v>25.85469632596541</v>
       </c>
       <c r="D21">
-        <v>6.87011453477936</v>
+        <v>6.878696325965414</v>
       </c>
       <c r="E21">
-        <v>4.082800000000001</v>
+        <v>4.404000000000002</v>
       </c>
       <c r="F21">
-        <v>6.102800000000001</v>
+        <v>6.424000000000001</v>
       </c>
       <c r="G21">
         <v>25.4</v>
@@ -3009,28 +3009,28 @@
         <v>2.46</v>
       </c>
       <c r="M21">
-        <v>0.33138204</v>
+        <v>0.3488232000000001</v>
       </c>
       <c r="N21">
-        <v>2.12861796</v>
+        <v>2.1111768</v>
       </c>
       <c r="O21">
-        <v>0.5747268491999999</v>
+        <v>0.5700177360000001</v>
       </c>
       <c r="P21">
-        <v>1.5538911108</v>
+        <v>1.541159064</v>
       </c>
       <c r="Q21">
-        <v>1.6938911108</v>
+        <v>1.681159064</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1371611458134872</v>
+        <v>0.1380398961619093</v>
       </c>
       <c r="T21">
-        <v>1.094482985319815</v>
+        <v>1.105010188061507</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.423456020730633</v>
+        <v>7.052283219694102</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1183597169295275</v>
+        <v>0.1180874957501303</v>
       </c>
       <c r="C22">
-        <v>25.85469632596541</v>
+        <v>25.5420995838245</v>
       </c>
       <c r="D22">
-        <v>6.878696325965414</v>
+        <v>6.887299583824503</v>
       </c>
       <c r="E22">
-        <v>4.404000000000002</v>
+        <v>4.725200000000001</v>
       </c>
       <c r="F22">
-        <v>6.424000000000001</v>
+        <v>6.745200000000001</v>
       </c>
       <c r="G22">
         <v>25.4</v>
@@ -3091,28 +3091,28 @@
         <v>2.46</v>
       </c>
       <c r="M22">
-        <v>0.3488232000000001</v>
+        <v>0.3662643600000001</v>
       </c>
       <c r="N22">
-        <v>2.1111768</v>
+        <v>2.09373564</v>
       </c>
       <c r="O22">
-        <v>0.5700177360000001</v>
+        <v>0.5653086227999999</v>
       </c>
       <c r="P22">
-        <v>1.541159064</v>
+        <v>1.5284270172</v>
       </c>
       <c r="Q22">
-        <v>1.681159064</v>
+        <v>1.6684270172</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1380398961619093</v>
+        <v>0.1389408933545953</v>
       </c>
       <c r="T22">
-        <v>1.105010188061507</v>
+        <v>1.115803902265014</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>7.052283219694102</v>
+        <v>6.716460209232477</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1180874957501303</v>
+        <v>0.1178152745707331</v>
       </c>
       <c r="C23">
-        <v>25.5420995838245</v>
+        <v>25.22952438900327</v>
       </c>
       <c r="D23">
-        <v>6.887299583824503</v>
+        <v>6.895924389003274</v>
       </c>
       <c r="E23">
-        <v>4.725200000000001</v>
+        <v>5.0464</v>
       </c>
       <c r="F23">
-        <v>6.745200000000001</v>
+        <v>7.066400000000001</v>
       </c>
       <c r="G23">
         <v>25.4</v>
@@ -3173,28 +3173,28 @@
         <v>2.46</v>
       </c>
       <c r="M23">
-        <v>0.36626436</v>
+        <v>0.38370552</v>
       </c>
       <c r="N23">
-        <v>2.09373564</v>
+        <v>2.07629448</v>
       </c>
       <c r="O23">
-        <v>0.5653086227999999</v>
+        <v>0.5605995096</v>
       </c>
       <c r="P23">
-        <v>1.5284270172</v>
+        <v>1.5156949704</v>
       </c>
       <c r="Q23">
-        <v>1.6684270172</v>
+        <v>1.6556949704</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1389408933545953</v>
+        <v>0.1398649930394014</v>
       </c>
       <c r="T23">
-        <v>1.115803902265014</v>
+        <v>1.126874378371175</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.716460209232478</v>
+        <v>6.411166563358275</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1178152745707331</v>
+        <v>0.117543053391336</v>
       </c>
       <c r="C24">
-        <v>25.22952438900327</v>
+        <v>24.91697082255284</v>
       </c>
       <c r="D24">
-        <v>6.895924389003274</v>
+        <v>6.904570822552847</v>
       </c>
       <c r="E24">
-        <v>5.0464</v>
+        <v>5.367600000000001</v>
       </c>
       <c r="F24">
-        <v>7.066400000000001</v>
+        <v>7.387600000000002</v>
       </c>
       <c r="G24">
         <v>25.4</v>
@@ -3255,28 +3255,28 @@
         <v>2.46</v>
       </c>
       <c r="M24">
-        <v>0.38370552</v>
+        <v>0.4011466800000001</v>
       </c>
       <c r="N24">
-        <v>2.07629448</v>
+        <v>2.05885332</v>
       </c>
       <c r="O24">
-        <v>0.5605995096</v>
+        <v>0.5558903964</v>
       </c>
       <c r="P24">
-        <v>1.5156949704</v>
+        <v>1.5029629236</v>
       </c>
       <c r="Q24">
-        <v>1.6556949704</v>
+        <v>1.6429629236</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1398649930394014</v>
+        <v>0.1408130953134233</v>
       </c>
       <c r="T24">
-        <v>1.126874378371175</v>
+        <v>1.138232399311263</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.411166563358275</v>
+        <v>6.132420191038349</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.117543053391336</v>
+        <v>0.1174460322119388</v>
       </c>
       <c r="C25">
-        <v>24.91697082255284</v>
+        <v>24.59885770409807</v>
       </c>
       <c r="D25">
-        <v>6.904570822552847</v>
+        <v>6.907657704098072</v>
       </c>
       <c r="E25">
-        <v>5.367600000000001</v>
+        <v>5.688800000000002</v>
       </c>
       <c r="F25">
-        <v>7.387600000000002</v>
+        <v>7.708800000000002</v>
       </c>
       <c r="G25">
         <v>25.4</v>
@@ -3337,45 +3337,45 @@
         <v>2.46</v>
       </c>
       <c r="M25">
-        <v>0.4011466800000001</v>
+        <v>0.4262966400000001</v>
       </c>
       <c r="N25">
-        <v>2.05885332</v>
+        <v>2.03370336</v>
       </c>
       <c r="O25">
-        <v>0.5558903964</v>
+        <v>0.5490999071999999</v>
       </c>
       <c r="P25">
-        <v>1.5029629236</v>
+        <v>1.4846034528</v>
       </c>
       <c r="Q25">
-        <v>1.6429629236</v>
+        <v>1.6246034528</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1408130953134233</v>
+        <v>0.1417861476472879</v>
       </c>
       <c r="T25">
-        <v>1.138232399311263</v>
+        <v>1.149889315539247</v>
       </c>
       <c r="U25">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V25">
         <v>0.27</v>
       </c>
       <c r="W25">
-        <v>0.039639</v>
+        <v>0.040369</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y25">
-        <v>6.132420191038349</v>
+        <v>5.770629578501953</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1174460322119388</v>
+        <v>0.1171811110325416</v>
       </c>
       <c r="C26">
-        <v>24.59885770409807</v>
+        <v>24.28610066370742</v>
       </c>
       <c r="D26">
-        <v>6.907657704098072</v>
+        <v>6.916100663707424</v>
       </c>
       <c r="E26">
-        <v>5.688800000000001</v>
+        <v>6.010000000000002</v>
       </c>
       <c r="F26">
-        <v>7.708800000000001</v>
+        <v>8.030000000000001</v>
       </c>
       <c r="G26">
         <v>25.4</v>
@@ -3419,28 +3419,28 @@
         <v>2.46</v>
       </c>
       <c r="M26">
-        <v>0.4262966400000001</v>
+        <v>0.4440590000000001</v>
       </c>
       <c r="N26">
-        <v>2.03370336</v>
+        <v>2.015941</v>
       </c>
       <c r="O26">
-        <v>0.5490999072</v>
+        <v>0.5443040699999999</v>
       </c>
       <c r="P26">
-        <v>1.4846034528</v>
+        <v>1.47163693</v>
       </c>
       <c r="Q26">
-        <v>1.6246034528</v>
+        <v>1.61163693</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1417861476472879</v>
+        <v>0.1427851480433888</v>
       </c>
       <c r="T26">
-        <v>1.149889315539247</v>
+        <v>1.161857082866645</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.770629578501955</v>
+        <v>5.539804395361876</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1171811110325416</v>
+        <v>0.1169161898531444</v>
       </c>
       <c r="C27">
-        <v>24.28610066370742</v>
+        <v>23.97336428757194</v>
       </c>
       <c r="D27">
-        <v>6.916100663707424</v>
+        <v>6.924564287571946</v>
       </c>
       <c r="E27">
-        <v>6.010000000000002</v>
+        <v>6.331200000000003</v>
       </c>
       <c r="F27">
-        <v>8.030000000000001</v>
+        <v>8.351200000000002</v>
       </c>
       <c r="G27">
         <v>25.4</v>
@@ -3501,28 +3501,28 @@
         <v>2.46</v>
       </c>
       <c r="M27">
-        <v>0.4440590000000001</v>
+        <v>0.4618213600000001</v>
       </c>
       <c r="N27">
-        <v>2.015941</v>
+        <v>1.99817864</v>
       </c>
       <c r="O27">
-        <v>0.5443040699999999</v>
+        <v>0.5395082328</v>
       </c>
       <c r="P27">
-        <v>1.47163693</v>
+        <v>1.4586704072</v>
       </c>
       <c r="Q27">
-        <v>1.61163693</v>
+        <v>1.5986704072</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1427851480433888</v>
+        <v>0.1438111484501952</v>
       </c>
       <c r="T27">
-        <v>1.161857082866645</v>
+        <v>1.174148303365052</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.539804395361876</v>
+        <v>5.326734995540265</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1169161898531444</v>
+        <v>0.1166512686737473</v>
       </c>
       <c r="C28">
-        <v>23.97336428757194</v>
+        <v>23.66064865164864</v>
       </c>
       <c r="D28">
-        <v>6.924564287571946</v>
+        <v>6.93304865164864</v>
       </c>
       <c r="E28">
-        <v>6.331200000000003</v>
+        <v>6.652400000000002</v>
       </c>
       <c r="F28">
-        <v>8.351200000000002</v>
+        <v>8.672400000000001</v>
       </c>
       <c r="G28">
         <v>25.4</v>
@@ -3583,28 +3583,28 @@
         <v>2.46</v>
       </c>
       <c r="M28">
-        <v>0.4618213600000001</v>
+        <v>0.4795837200000001</v>
       </c>
       <c r="N28">
-        <v>1.99817864</v>
+        <v>1.98041628</v>
       </c>
       <c r="O28">
-        <v>0.5395082328</v>
+        <v>0.5347123955999999</v>
       </c>
       <c r="P28">
-        <v>1.4586704072</v>
+        <v>1.4457038844</v>
       </c>
       <c r="Q28">
-        <v>1.5986704072</v>
+        <v>1.5857038844</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1438111484501952</v>
+        <v>0.144865258457188</v>
       </c>
       <c r="T28">
-        <v>1.174148303365052</v>
+        <v>1.18677626963054</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.326734995540265</v>
+        <v>5.129448514223959</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1166512686737473</v>
+        <v>0.1163863474943501</v>
       </c>
       <c r="C29">
-        <v>23.66064865164864</v>
+        <v>23.34795383226724</v>
       </c>
       <c r="D29">
-        <v>6.93304865164864</v>
+        <v>6.941553832267245</v>
       </c>
       <c r="E29">
-        <v>6.652400000000002</v>
+        <v>6.973600000000003</v>
       </c>
       <c r="F29">
-        <v>8.672400000000001</v>
+        <v>8.993600000000002</v>
       </c>
       <c r="G29">
         <v>25.4</v>
@@ -3665,28 +3665,28 @@
         <v>2.46</v>
       </c>
       <c r="M29">
-        <v>0.4795837200000001</v>
+        <v>0.4973460800000001</v>
       </c>
       <c r="N29">
-        <v>1.98041628</v>
+        <v>1.96265392</v>
       </c>
       <c r="O29">
-        <v>0.5347123955999999</v>
+        <v>0.5299165584</v>
       </c>
       <c r="P29">
-        <v>1.4457038844</v>
+        <v>1.4327373616</v>
       </c>
       <c r="Q29">
-        <v>1.5857038844</v>
+        <v>1.5727373616</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.144865258457188</v>
+        <v>0.1459486492977085</v>
       </c>
       <c r="T29">
-        <v>1.18677626963054</v>
+        <v>1.199755012736736</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.129448514223959</v>
+        <v>4.946253924430247</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1163863474943501</v>
+        <v>0.1161214263149529</v>
       </c>
       <c r="C30">
-        <v>23.34795383226724</v>
+        <v>23.0352799061325</v>
       </c>
       <c r="D30">
-        <v>6.941553832267245</v>
+        <v>6.950079906132504</v>
       </c>
       <c r="E30">
-        <v>6.973600000000003</v>
+        <v>7.294800000000002</v>
       </c>
       <c r="F30">
-        <v>8.993600000000002</v>
+        <v>9.314800000000002</v>
       </c>
       <c r="G30">
         <v>25.4</v>
@@ -3747,28 +3747,28 @@
         <v>2.46</v>
       </c>
       <c r="M30">
-        <v>0.4973460800000001</v>
+        <v>0.5151084400000001</v>
       </c>
       <c r="N30">
-        <v>1.96265392</v>
+        <v>1.94489156</v>
       </c>
       <c r="O30">
-        <v>0.5299165584</v>
+        <v>0.5251207212</v>
       </c>
       <c r="P30">
-        <v>1.4327373616</v>
+        <v>1.4197708388</v>
       </c>
       <c r="Q30">
-        <v>1.5727373616</v>
+        <v>1.5597708388</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1459486492977085</v>
+        <v>0.1470625581900745</v>
       </c>
       <c r="T30">
-        <v>1.199755012736736</v>
+        <v>1.213099354240289</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.946253924430247</v>
+        <v>4.775693444277479</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1161214263149529</v>
+        <v>0.1158565051355558</v>
       </c>
       <c r="C31">
-        <v>23.0352799061325</v>
+        <v>22.72262695032648</v>
       </c>
       <c r="D31">
-        <v>6.950079906132504</v>
+        <v>6.958626950326481</v>
       </c>
       <c r="E31">
-        <v>7.2948</v>
+        <v>7.616000000000001</v>
       </c>
       <c r="F31">
-        <v>9.3148</v>
+        <v>9.636000000000001</v>
       </c>
       <c r="G31">
         <v>25.4</v>
@@ -3829,28 +3829,28 @@
         <v>2.46</v>
       </c>
       <c r="M31">
-        <v>0.51510844</v>
+        <v>0.5328708000000001</v>
       </c>
       <c r="N31">
-        <v>1.94489156</v>
+        <v>1.9271292</v>
       </c>
       <c r="O31">
-        <v>0.5251207212</v>
+        <v>0.520324884</v>
       </c>
       <c r="P31">
-        <v>1.4197708388</v>
+        <v>1.406804316</v>
       </c>
       <c r="Q31">
-        <v>1.5597708388</v>
+        <v>1.546804316</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1470625581900745</v>
+        <v>0.1482082930507939</v>
       </c>
       <c r="T31">
-        <v>1.213099354240289</v>
+        <v>1.226824962643944</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.775693444277481</v>
+        <v>4.616503662801565</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1158565051355558</v>
+        <v>0.1161573339561586</v>
       </c>
       <c r="C32">
-        <v>22.72262695032648</v>
+        <v>22.39172304802549</v>
       </c>
       <c r="D32">
-        <v>6.958626950326481</v>
+        <v>6.948923048025489</v>
       </c>
       <c r="E32">
-        <v>7.616000000000001</v>
+        <v>7.937200000000002</v>
       </c>
       <c r="F32">
-        <v>9.636000000000001</v>
+        <v>9.957200000000002</v>
       </c>
       <c r="G32">
         <v>25.4</v>
@@ -3911,45 +3911,45 @@
         <v>2.46</v>
       </c>
       <c r="M32">
-        <v>0.5328708000000001</v>
+        <v>0.5755261600000001</v>
       </c>
       <c r="N32">
-        <v>1.9271292</v>
+        <v>1.88447384</v>
       </c>
       <c r="O32">
-        <v>0.520324884</v>
+        <v>0.5088079368</v>
       </c>
       <c r="P32">
-        <v>1.406804316</v>
+        <v>1.3756659032</v>
       </c>
       <c r="Q32">
-        <v>1.546804316</v>
+        <v>1.5156659032</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1482082930507939</v>
+        <v>0.1493872376176211</v>
       </c>
       <c r="T32">
-        <v>1.226824962643944</v>
+        <v>1.240948414769444</v>
       </c>
       <c r="U32">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V32">
         <v>0.27</v>
       </c>
       <c r="W32">
-        <v>0.040369</v>
+        <v>0.042194</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y32">
-        <v>4.616503662801565</v>
+        <v>4.274349579522154</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1161573339561586</v>
+        <v>0.1159106627767614</v>
       </c>
       <c r="C33">
-        <v>22.39172304802549</v>
+        <v>22.07847797533909</v>
       </c>
       <c r="D33">
-        <v>6.948923048025489</v>
+        <v>6.956877975339094</v>
       </c>
       <c r="E33">
-        <v>7.937200000000002</v>
+        <v>8.258400000000002</v>
       </c>
       <c r="F33">
-        <v>9.957200000000002</v>
+        <v>10.2784</v>
       </c>
       <c r="G33">
         <v>25.4</v>
@@ -3993,28 +3993,28 @@
         <v>2.46</v>
       </c>
       <c r="M33">
-        <v>0.5755261600000001</v>
+        <v>0.5940915200000001</v>
       </c>
       <c r="N33">
-        <v>1.88447384</v>
+        <v>1.86590848</v>
       </c>
       <c r="O33">
-        <v>0.5088079368</v>
+        <v>0.5037952896</v>
       </c>
       <c r="P33">
-        <v>1.3756659032</v>
+        <v>1.3621131904</v>
       </c>
       <c r="Q33">
-        <v>1.5156659032</v>
+        <v>1.5021131904</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1493872376176211</v>
+        <v>0.1506008570246491</v>
       </c>
       <c r="T33">
-        <v>1.240948414769444</v>
+        <v>1.255487262545694</v>
       </c>
       <c r="U33">
         <v>0.0578</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.274349579522154</v>
+        <v>4.140776155162087</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1159106627767614</v>
+        <v>0.1156639915973642</v>
       </c>
       <c r="C34">
-        <v>22.07847797533909</v>
+        <v>21.76525113667062</v>
       </c>
       <c r="D34">
-        <v>6.956877975339094</v>
+        <v>6.964851136670624</v>
       </c>
       <c r="E34">
-        <v>8.258400000000002</v>
+        <v>8.579600000000003</v>
       </c>
       <c r="F34">
-        <v>10.2784</v>
+        <v>10.5996</v>
       </c>
       <c r="G34">
         <v>25.4</v>
@@ -4075,28 +4075,28 @@
         <v>2.46</v>
       </c>
       <c r="M34">
-        <v>0.5940915200000001</v>
+        <v>0.6126568800000002</v>
       </c>
       <c r="N34">
-        <v>1.86590848</v>
+        <v>1.84734312</v>
       </c>
       <c r="O34">
-        <v>0.5037952896</v>
+        <v>0.4987826423999999</v>
       </c>
       <c r="P34">
-        <v>1.3621131904</v>
+        <v>1.3485604776</v>
       </c>
       <c r="Q34">
-        <v>1.5021131904</v>
+        <v>1.4885604776</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1506008570246491</v>
+        <v>0.1518507038766631</v>
       </c>
       <c r="T34">
-        <v>1.255487262545694</v>
+        <v>1.270460105777952</v>
       </c>
       <c r="U34">
         <v>0.0578</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.140776155162087</v>
+        <v>4.015298089854143</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1156639915973642</v>
+        <v>0.1162860204179671</v>
       </c>
       <c r="C35">
-        <v>21.76525113667062</v>
+        <v>21.42398024020513</v>
       </c>
       <c r="D35">
-        <v>6.964851136670624</v>
+        <v>6.944780240205129</v>
       </c>
       <c r="E35">
-        <v>8.579600000000003</v>
+        <v>8.900800000000002</v>
       </c>
       <c r="F35">
-        <v>10.5996</v>
+        <v>10.9208</v>
       </c>
       <c r="G35">
         <v>25.4</v>
@@ -4157,45 +4157,45 @@
         <v>2.46</v>
       </c>
       <c r="M35">
-        <v>0.6126568800000002</v>
+        <v>0.6694450400000002</v>
       </c>
       <c r="N35">
-        <v>1.84734312</v>
+        <v>1.79055496</v>
       </c>
       <c r="O35">
-        <v>0.4987826423999999</v>
+        <v>0.4834498392</v>
       </c>
       <c r="P35">
-        <v>1.3485604776</v>
+        <v>1.3071051208</v>
       </c>
       <c r="Q35">
-        <v>1.4885604776</v>
+        <v>1.4471051208</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1518507038766631</v>
+        <v>0.1531384248757077</v>
       </c>
       <c r="T35">
-        <v>1.270460105777952</v>
+        <v>1.285886671532399</v>
       </c>
       <c r="U35">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V35">
         <v>0.27</v>
       </c>
       <c r="W35">
-        <v>0.042194</v>
+        <v>0.044749</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y35">
-        <v>4.015298089854143</v>
+        <v>3.674685527582667</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1162860204179671</v>
+        <v>0.1160648992385699</v>
       </c>
       <c r="C36">
-        <v>21.42398024020513</v>
+        <v>21.10990185368594</v>
       </c>
       <c r="D36">
-        <v>6.944780240205129</v>
+        <v>6.951901853685944</v>
       </c>
       <c r="E36">
-        <v>8.900800000000002</v>
+        <v>9.222000000000003</v>
       </c>
       <c r="F36">
-        <v>10.9208</v>
+        <v>11.242</v>
       </c>
       <c r="G36">
         <v>25.4</v>
@@ -4239,28 +4239,28 @@
         <v>2.46</v>
       </c>
       <c r="M36">
-        <v>0.6694450400000002</v>
+        <v>0.6891346000000002</v>
       </c>
       <c r="N36">
-        <v>1.79055496</v>
+        <v>1.7708654</v>
       </c>
       <c r="O36">
-        <v>0.4834498392</v>
+        <v>0.478133658</v>
       </c>
       <c r="P36">
-        <v>1.3071051208</v>
+        <v>1.292731742</v>
       </c>
       <c r="Q36">
-        <v>1.4471051208</v>
+        <v>1.432731742</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1531384248757077</v>
+        <v>0.1544657680593383</v>
       </c>
       <c r="T36">
-        <v>1.285886671532399</v>
+        <v>1.301787900848521</v>
       </c>
       <c r="U36">
         <v>0.0613</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.674685527582667</v>
+        <v>3.569694512508876</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1160648992385699</v>
+        <v>0.1165796180591727</v>
       </c>
       <c r="C37">
-        <v>21.10990185368594</v>
+        <v>20.77214690696991</v>
       </c>
       <c r="D37">
-        <v>6.951901853685944</v>
+        <v>6.93534690696991</v>
       </c>
       <c r="E37">
-        <v>9.222000000000003</v>
+        <v>9.543200000000004</v>
       </c>
       <c r="F37">
-        <v>11.242</v>
+        <v>11.5632</v>
       </c>
       <c r="G37">
         <v>25.4</v>
@@ -4321,45 +4321,45 @@
         <v>2.46</v>
       </c>
       <c r="M37">
-        <v>0.6891346000000002</v>
+        <v>0.7412011200000003</v>
       </c>
       <c r="N37">
-        <v>1.7708654</v>
+        <v>1.71879888</v>
       </c>
       <c r="O37">
-        <v>0.478133658</v>
+        <v>0.4640756975999999</v>
       </c>
       <c r="P37">
-        <v>1.292731742</v>
+        <v>1.2547231824</v>
       </c>
       <c r="Q37">
-        <v>1.432731742</v>
+        <v>1.3947231824</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1544657680593383</v>
+        <v>0.1558345907174574</v>
       </c>
       <c r="T37">
-        <v>1.301787900848521</v>
+        <v>1.318186043580772</v>
       </c>
       <c r="U37">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V37">
         <v>0.27</v>
       </c>
       <c r="W37">
-        <v>0.044749</v>
+        <v>0.046793</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y37">
-        <v>3.569694512508876</v>
+        <v>3.318937240677671</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1165796180591727</v>
+        <v>0.1163789368797755</v>
       </c>
       <c r="C38">
-        <v>20.7721469069699</v>
+        <v>20.45739204690204</v>
       </c>
       <c r="D38">
-        <v>6.935346906969908</v>
+        <v>6.941792046902036</v>
       </c>
       <c r="E38">
-        <v>9.543200000000002</v>
+        <v>9.864400000000002</v>
       </c>
       <c r="F38">
-        <v>11.5632</v>
+        <v>11.8844</v>
       </c>
       <c r="G38">
         <v>25.4</v>
@@ -4403,28 +4403,28 @@
         <v>2.46</v>
       </c>
       <c r="M38">
-        <v>0.7412011200000002</v>
+        <v>0.7617900400000002</v>
       </c>
       <c r="N38">
-        <v>1.71879888</v>
+        <v>1.69820996</v>
       </c>
       <c r="O38">
-        <v>0.4640756976</v>
+        <v>0.4585166892</v>
       </c>
       <c r="P38">
-        <v>1.2547231824</v>
+        <v>1.2396932708</v>
       </c>
       <c r="Q38">
-        <v>1.3947231824</v>
+        <v>1.3796932708</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1558345907174574</v>
+        <v>0.1572468680631358</v>
       </c>
       <c r="T38">
-        <v>1.318186043580772</v>
+        <v>1.335104762272777</v>
       </c>
       <c r="U38">
         <v>0.0641</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.318937240677671</v>
+        <v>3.229236234172869</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1163789368797755</v>
+        <v>0.1161782557003784</v>
       </c>
       <c r="C39">
-        <v>20.45739204690204</v>
+        <v>20.14264917714089</v>
       </c>
       <c r="D39">
-        <v>6.941792046902036</v>
+        <v>6.948249177140892</v>
       </c>
       <c r="E39">
-        <v>9.864400000000002</v>
+        <v>10.1856</v>
       </c>
       <c r="F39">
-        <v>11.8844</v>
+        <v>12.2056</v>
       </c>
       <c r="G39">
         <v>25.4</v>
@@ -4485,28 +4485,28 @@
         <v>2.46</v>
       </c>
       <c r="M39">
-        <v>0.7617900400000002</v>
+        <v>0.7823789600000002</v>
       </c>
       <c r="N39">
-        <v>1.69820996</v>
+        <v>1.67762104</v>
       </c>
       <c r="O39">
-        <v>0.4585166892</v>
+        <v>0.4529576808</v>
       </c>
       <c r="P39">
-        <v>1.2396932708</v>
+        <v>1.2246633592</v>
       </c>
       <c r="Q39">
-        <v>1.3796932708</v>
+        <v>1.3646633592</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1572468680631358</v>
+        <v>0.1587047027425458</v>
       </c>
       <c r="T39">
-        <v>1.335104762272777</v>
+        <v>1.35256924608388</v>
       </c>
       <c r="U39">
         <v>0.0641</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.229236234172869</v>
+        <v>3.144256333273583</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1161782557003784</v>
+        <v>0.1159775745209812</v>
       </c>
       <c r="C40">
-        <v>20.14264917714089</v>
+        <v>19.82791833117714</v>
       </c>
       <c r="D40">
-        <v>6.948249177140892</v>
+        <v>6.954718331177137</v>
       </c>
       <c r="E40">
-        <v>10.1856</v>
+        <v>10.5068</v>
       </c>
       <c r="F40">
-        <v>12.2056</v>
+        <v>12.5268</v>
       </c>
       <c r="G40">
         <v>25.4</v>
@@ -4567,28 +4567,28 @@
         <v>2.46</v>
       </c>
       <c r="M40">
-        <v>0.7823789600000002</v>
+        <v>0.8029678800000002</v>
       </c>
       <c r="N40">
-        <v>1.67762104</v>
+        <v>1.65703212</v>
       </c>
       <c r="O40">
-        <v>0.4529576808</v>
+        <v>0.4473986724</v>
       </c>
       <c r="P40">
-        <v>1.2246633592</v>
+        <v>1.2096334476</v>
       </c>
       <c r="Q40">
-        <v>1.3646633592</v>
+        <v>1.3496334476</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1587047027425458</v>
+        <v>0.160210335280297</v>
       </c>
       <c r="T40">
-        <v>1.35256924608388</v>
+        <v>1.370606335921575</v>
       </c>
       <c r="U40">
         <v>0.0641</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.144256333273583</v>
+        <v>3.063634376010158</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1159775745209812</v>
+        <v>0.118054493341584</v>
       </c>
       <c r="C41">
-        <v>19.82791833117714</v>
+        <v>19.44034405235304</v>
       </c>
       <c r="D41">
-        <v>6.954718331177137</v>
+        <v>6.888344052353044</v>
       </c>
       <c r="E41">
-        <v>10.5068</v>
+        <v>10.828</v>
       </c>
       <c r="F41">
-        <v>12.5268</v>
+        <v>12.848</v>
       </c>
       <c r="G41">
         <v>25.4</v>
@@ -4649,45 +4649,45 @@
         <v>2.46</v>
       </c>
       <c r="M41">
-        <v>0.8029678800000002</v>
+        <v>0.9237712000000002</v>
       </c>
       <c r="N41">
-        <v>1.65703212</v>
+        <v>1.5362288</v>
       </c>
       <c r="O41">
-        <v>0.4473986724</v>
+        <v>0.4147817759999999</v>
       </c>
       <c r="P41">
-        <v>1.2096334476</v>
+        <v>1.121447024</v>
       </c>
       <c r="Q41">
-        <v>1.3496334476</v>
+        <v>1.261447024</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.160210335280297</v>
+        <v>0.1617661555693067</v>
       </c>
       <c r="T41">
-        <v>1.370606335921575</v>
+        <v>1.389244662087194</v>
       </c>
       <c r="U41">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V41">
         <v>0.27</v>
       </c>
       <c r="W41">
-        <v>0.046793</v>
+        <v>0.05248700000000001</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y41">
-        <v>3.063634376010158</v>
+        <v>2.662997071136229</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.118054493341584</v>
+        <v>0.1179107521621869</v>
       </c>
       <c r="C42">
-        <v>19.44034405235304</v>
+        <v>19.12369690647087</v>
       </c>
       <c r="D42">
-        <v>6.888344052353044</v>
+        <v>6.892896906470875</v>
       </c>
       <c r="E42">
-        <v>10.828</v>
+        <v>11.1492</v>
       </c>
       <c r="F42">
-        <v>12.848</v>
+        <v>13.1692</v>
       </c>
       <c r="G42">
         <v>25.4</v>
@@ -4731,28 +4731,28 @@
         <v>2.46</v>
       </c>
       <c r="M42">
-        <v>0.9237712000000002</v>
+        <v>0.9468654800000004</v>
       </c>
       <c r="N42">
-        <v>1.5362288</v>
+        <v>1.513134519999999</v>
       </c>
       <c r="O42">
-        <v>0.4147817759999999</v>
+        <v>0.4085463203999999</v>
       </c>
       <c r="P42">
-        <v>1.121447024</v>
+        <v>1.1045881996</v>
       </c>
       <c r="Q42">
-        <v>1.261447024</v>
+        <v>1.2445881996</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1617661555693067</v>
+        <v>0.1633747155291303</v>
       </c>
       <c r="T42">
-        <v>1.389244662087194</v>
+        <v>1.408514795919444</v>
       </c>
       <c r="U42">
         <v>0.07190000000000001</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.662997071136229</v>
+        <v>2.598045923059735</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1179107521621869</v>
+        <v>0.1177670109827897</v>
       </c>
       <c r="C43">
-        <v>19.12369690647087</v>
+        <v>18.80705578299119</v>
       </c>
       <c r="D43">
-        <v>6.892896906470875</v>
+        <v>6.897455782991192</v>
       </c>
       <c r="E43">
-        <v>11.1492</v>
+        <v>11.4704</v>
       </c>
       <c r="F43">
-        <v>13.1692</v>
+        <v>13.4904</v>
       </c>
       <c r="G43">
         <v>25.4</v>
@@ -4813,28 +4813,28 @@
         <v>2.46</v>
       </c>
       <c r="M43">
-        <v>0.9468654800000004</v>
+        <v>0.9699597600000003</v>
       </c>
       <c r="N43">
-        <v>1.513134519999999</v>
+        <v>1.49004024</v>
       </c>
       <c r="O43">
-        <v>0.4085463203999999</v>
+        <v>0.4023108647999999</v>
       </c>
       <c r="P43">
-        <v>1.1045881996</v>
+        <v>1.0877293752</v>
       </c>
       <c r="Q43">
-        <v>1.2445881996</v>
+        <v>1.2277293752</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1633747155291303</v>
+        <v>0.1650387430737754</v>
       </c>
       <c r="T43">
-        <v>1.408514795919444</v>
+        <v>1.42844941712522</v>
       </c>
       <c r="U43">
         <v>0.07190000000000001</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.598045923059735</v>
+        <v>2.536187686796408</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1177670109827897</v>
+        <v>0.1188474798033925</v>
       </c>
       <c r="C44">
-        <v>18.80705578299119</v>
+        <v>18.45173474280567</v>
       </c>
       <c r="D44">
-        <v>6.897455782991192</v>
+        <v>6.863334742805679</v>
       </c>
       <c r="E44">
-        <v>11.4704</v>
+        <v>11.7916</v>
       </c>
       <c r="F44">
-        <v>13.4904</v>
+        <v>13.8116</v>
       </c>
       <c r="G44">
         <v>25.4</v>
@@ -4895,45 +4895,45 @@
         <v>2.46</v>
       </c>
       <c r="M44">
-        <v>0.9699597600000002</v>
+        <v>1.04691928</v>
       </c>
       <c r="N44">
-        <v>1.49004024</v>
+        <v>1.41308072</v>
       </c>
       <c r="O44">
-        <v>0.4023108648</v>
+        <v>0.3815317944</v>
       </c>
       <c r="P44">
-        <v>1.0877293752</v>
+        <v>1.0315489256</v>
       </c>
       <c r="Q44">
-        <v>1.2277293752</v>
+        <v>1.1715489256</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1650387430737753</v>
+        <v>0.1667611575498114</v>
       </c>
       <c r="T44">
-        <v>1.42844941712522</v>
+        <v>1.449083498724181</v>
       </c>
       <c r="U44">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V44">
         <v>0.27</v>
       </c>
       <c r="W44">
-        <v>0.05248700000000001</v>
+        <v>0.055334</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y44">
-        <v>2.536187686796409</v>
+        <v>2.349751358098974</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1188474798033925</v>
+        <v>0.1187322086239954</v>
       </c>
       <c r="C45">
-        <v>18.45173474280567</v>
+        <v>18.13415889379273</v>
       </c>
       <c r="D45">
-        <v>6.863334742805679</v>
+        <v>6.866958893792732</v>
       </c>
       <c r="E45">
-        <v>11.7916</v>
+        <v>12.1128</v>
       </c>
       <c r="F45">
-        <v>13.8116</v>
+        <v>14.1328</v>
       </c>
       <c r="G45">
         <v>25.4</v>
@@ -4977,28 +4977,28 @@
         <v>2.46</v>
       </c>
       <c r="M45">
-        <v>1.04691928</v>
+        <v>1.07126624</v>
       </c>
       <c r="N45">
-        <v>1.41308072</v>
+        <v>1.38873376</v>
       </c>
       <c r="O45">
-        <v>0.3815317944</v>
+        <v>0.3749581152</v>
       </c>
       <c r="P45">
-        <v>1.0315489256</v>
+        <v>1.0137756448</v>
       </c>
       <c r="Q45">
-        <v>1.1715489256</v>
+        <v>1.1537756448</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1667611575498114</v>
+        <v>0.1685450868285631</v>
       </c>
       <c r="T45">
-        <v>1.449083498724181</v>
+        <v>1.470454511808819</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.349751358098974</v>
+        <v>2.296347918142179</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1187322086239954</v>
+        <v>0.1186169374445982</v>
       </c>
       <c r="C46">
-        <v>18.13415889379273</v>
+        <v>17.816586874233</v>
       </c>
       <c r="D46">
-        <v>6.866958893792732</v>
+        <v>6.870586874232997</v>
       </c>
       <c r="E46">
-        <v>12.1128</v>
+        <v>12.434</v>
       </c>
       <c r="F46">
-        <v>14.1328</v>
+        <v>14.454</v>
       </c>
       <c r="G46">
         <v>25.4</v>
@@ -5059,28 +5059,28 @@
         <v>2.46</v>
       </c>
       <c r="M46">
-        <v>1.07126624</v>
+        <v>1.0956132</v>
       </c>
       <c r="N46">
-        <v>1.38873376</v>
+        <v>1.3643868</v>
       </c>
       <c r="O46">
-        <v>0.3749581152</v>
+        <v>0.3683844359999999</v>
       </c>
       <c r="P46">
-        <v>1.0137756448</v>
+        <v>0.9960023639999998</v>
       </c>
       <c r="Q46">
-        <v>1.1537756448</v>
+        <v>1.136002364</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1685450868285631</v>
+        <v>0.1703938862629058</v>
       </c>
       <c r="T46">
-        <v>1.470454511808819</v>
+        <v>1.492602652641989</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.296347918142179</v>
+        <v>2.245317964405686</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1186169374445982</v>
+        <v>0.118501666265201</v>
       </c>
       <c r="C47">
-        <v>17.816586874233</v>
+        <v>17.49901869019925</v>
       </c>
       <c r="D47">
-        <v>6.870586874232997</v>
+        <v>6.874218690199259</v>
       </c>
       <c r="E47">
-        <v>12.434</v>
+        <v>12.7552</v>
       </c>
       <c r="F47">
-        <v>14.454</v>
+        <v>14.7752</v>
       </c>
       <c r="G47">
         <v>25.4</v>
@@ -5141,28 +5141,28 @@
         <v>2.46</v>
       </c>
       <c r="M47">
-        <v>1.0956132</v>
+        <v>1.11996016</v>
       </c>
       <c r="N47">
-        <v>1.3643868</v>
+        <v>1.34003984</v>
       </c>
       <c r="O47">
-        <v>0.3683844359999999</v>
+        <v>0.3618107567999999</v>
       </c>
       <c r="P47">
-        <v>0.9960023639999998</v>
+        <v>0.9782290831999996</v>
       </c>
       <c r="Q47">
-        <v>1.136002364</v>
+        <v>1.1182290832</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1703938862629058</v>
+        <v>0.1723111597503723</v>
       </c>
       <c r="T47">
-        <v>1.492602652641989</v>
+        <v>1.5155710949875</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.245317964405686</v>
+        <v>2.196506704309909</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.118501666265201</v>
+        <v>0.1183863950858039</v>
       </c>
       <c r="C48">
-        <v>17.49901869019925</v>
+        <v>17.18145434777715</v>
       </c>
       <c r="D48">
-        <v>6.874218690199259</v>
+        <v>6.877854347777152</v>
       </c>
       <c r="E48">
-        <v>12.7552</v>
+        <v>13.0764</v>
       </c>
       <c r="F48">
-        <v>14.7752</v>
+        <v>15.0964</v>
       </c>
       <c r="G48">
         <v>25.4</v>
@@ -5223,28 +5223,28 @@
         <v>2.46</v>
       </c>
       <c r="M48">
-        <v>1.11996016</v>
+        <v>1.14430712</v>
       </c>
       <c r="N48">
-        <v>1.34003984</v>
+        <v>1.31569288</v>
       </c>
       <c r="O48">
-        <v>0.3618107567999999</v>
+        <v>0.3552370775999999</v>
       </c>
       <c r="P48">
-        <v>0.9782290831999996</v>
+        <v>0.9604558023999997</v>
       </c>
       <c r="Q48">
-        <v>1.1182290832</v>
+        <v>1.1004558024</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1723111597503723</v>
+        <v>0.174300783180762</v>
       </c>
       <c r="T48">
-        <v>1.5155710949875</v>
+        <v>1.539406271006425</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.196506704309909</v>
+        <v>2.149772519111827</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1183863950858039</v>
+        <v>0.1182711239064067</v>
       </c>
       <c r="C49">
-        <v>17.18145434777715</v>
+        <v>16.86389385306519</v>
       </c>
       <c r="D49">
-        <v>6.877854347777152</v>
+        <v>6.881493853065194</v>
       </c>
       <c r="E49">
-        <v>13.0764</v>
+        <v>13.3976</v>
       </c>
       <c r="F49">
-        <v>15.0964</v>
+        <v>15.4176</v>
       </c>
       <c r="G49">
         <v>25.4</v>
@@ -5305,28 +5305,28 @@
         <v>2.46</v>
       </c>
       <c r="M49">
-        <v>1.14430712</v>
+        <v>1.16865408</v>
       </c>
       <c r="N49">
-        <v>1.31569288</v>
+        <v>1.291345919999999</v>
       </c>
       <c r="O49">
-        <v>0.3552370775999999</v>
+        <v>0.3486633983999999</v>
       </c>
       <c r="P49">
-        <v>0.9604558023999997</v>
+        <v>0.9426825215999997</v>
       </c>
       <c r="Q49">
-        <v>1.1004558024</v>
+        <v>1.0826825216</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.174300783180762</v>
+        <v>0.1763669305892436</v>
       </c>
       <c r="T49">
-        <v>1.539406271006425</v>
+        <v>1.56415818456454</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.149772519111827</v>
+        <v>2.10498559163033</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1182711239064067</v>
+        <v>0.1181558527270095</v>
       </c>
       <c r="C50">
-        <v>16.86389385306519</v>
+        <v>16.54633721217481</v>
       </c>
       <c r="D50">
-        <v>6.881493853065194</v>
+        <v>6.885137212174812</v>
       </c>
       <c r="E50">
-        <v>13.3976</v>
+        <v>13.7188</v>
       </c>
       <c r="F50">
-        <v>15.4176</v>
+        <v>15.7388</v>
       </c>
       <c r="G50">
         <v>25.4</v>
@@ -5387,28 +5387,28 @@
         <v>2.46</v>
       </c>
       <c r="M50">
-        <v>1.16865408</v>
+        <v>1.19300104</v>
       </c>
       <c r="N50">
-        <v>1.29134592</v>
+        <v>1.26699896</v>
       </c>
       <c r="O50">
-        <v>0.3486633983999999</v>
+        <v>0.3420897192</v>
       </c>
       <c r="P50">
-        <v>0.9426825215999998</v>
+        <v>0.9249092407999998</v>
       </c>
       <c r="Q50">
-        <v>1.0826825216</v>
+        <v>1.0649092408</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1763669305892436</v>
+        <v>0.1785141033862931</v>
       </c>
       <c r="T50">
-        <v>1.56415818456454</v>
+        <v>1.589880761399444</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.104985591630331</v>
+        <v>2.062026702005221</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1181558527270095</v>
+        <v>0.1180405815476123</v>
       </c>
       <c r="C51">
-        <v>16.54633721217481</v>
+        <v>16.22878443123038</v>
       </c>
       <c r="D51">
-        <v>6.885137212174812</v>
+        <v>6.888784431230386</v>
       </c>
       <c r="E51">
-        <v>13.7188</v>
+        <v>14.04</v>
       </c>
       <c r="F51">
-        <v>15.7388</v>
+        <v>16.06</v>
       </c>
       <c r="G51">
         <v>25.4</v>
@@ -5469,28 +5469,28 @@
         <v>2.46</v>
       </c>
       <c r="M51">
-        <v>1.19300104</v>
+        <v>1.217348</v>
       </c>
       <c r="N51">
-        <v>1.26699896</v>
+        <v>1.242652</v>
       </c>
       <c r="O51">
-        <v>0.3420897192</v>
+        <v>0.3355160399999999</v>
       </c>
       <c r="P51">
-        <v>0.9249092407999998</v>
+        <v>0.9071359599999997</v>
       </c>
       <c r="Q51">
-        <v>1.0649092408</v>
+        <v>1.04713596</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1785141033862931</v>
+        <v>0.1807471630952246</v>
       </c>
       <c r="T51">
-        <v>1.589880761399444</v>
+        <v>1.616632241307744</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.062026702005221</v>
+        <v>2.020786167965117</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1180405815476123</v>
+        <v>0.1232119703682152</v>
       </c>
       <c r="C52">
-        <v>16.22878443123038</v>
+        <v>15.74767353033237</v>
       </c>
       <c r="D52">
-        <v>6.888784431230386</v>
+        <v>6.728873530332374</v>
       </c>
       <c r="E52">
-        <v>14.04</v>
+        <v>14.3612</v>
       </c>
       <c r="F52">
-        <v>16.06</v>
+        <v>16.3812</v>
       </c>
       <c r="G52">
         <v>25.4</v>
@@ -5551,45 +5551,45 @@
         <v>2.46</v>
       </c>
       <c r="M52">
-        <v>1.217348</v>
+        <v>1.474308</v>
       </c>
       <c r="N52">
-        <v>1.242652</v>
+        <v>0.9856919999999998</v>
       </c>
       <c r="O52">
-        <v>0.3355160399999999</v>
+        <v>0.26613684</v>
       </c>
       <c r="P52">
-        <v>0.9071359599999997</v>
+        <v>0.7195551599999999</v>
       </c>
       <c r="Q52">
-        <v>1.04713596</v>
+        <v>0.85955516</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1807471630952246</v>
+        <v>0.1830713680983983</v>
       </c>
       <c r="T52">
-        <v>1.616632241307744</v>
+        <v>1.644475618355158</v>
       </c>
       <c r="U52">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V52">
         <v>0.27</v>
       </c>
       <c r="W52">
-        <v>0.055334</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y52">
-        <v>2.020786167965117</v>
+        <v>1.6685794284505</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1232119703682152</v>
+        <v>0.123200359188818</v>
       </c>
       <c r="C53">
-        <v>15.74767353033237</v>
+        <v>15.42682425767117</v>
       </c>
       <c r="D53">
-        <v>6.728873530332374</v>
+        <v>6.729224257671179</v>
       </c>
       <c r="E53">
-        <v>14.3612</v>
+        <v>14.6824</v>
       </c>
       <c r="F53">
-        <v>16.3812</v>
+        <v>16.7024</v>
       </c>
       <c r="G53">
         <v>25.4</v>
@@ -5633,28 +5633,28 @@
         <v>2.46</v>
       </c>
       <c r="M53">
-        <v>1.474308</v>
+        <v>1.503216</v>
       </c>
       <c r="N53">
-        <v>0.9856919999999998</v>
+        <v>0.9567839999999996</v>
       </c>
       <c r="O53">
-        <v>0.26613684</v>
+        <v>0.2583316799999999</v>
       </c>
       <c r="P53">
-        <v>0.7195551599999999</v>
+        <v>0.6984523199999997</v>
       </c>
       <c r="Q53">
-        <v>0.85955516</v>
+        <v>0.8384523199999998</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1830713680983983</v>
+        <v>0.1854924149767041</v>
       </c>
       <c r="T53">
-        <v>1.644475618355158</v>
+        <v>1.673479136112881</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.6685794284505</v>
+        <v>1.636491362518759</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.123200359188818</v>
+        <v>0.1231887480094208</v>
       </c>
       <c r="C54">
-        <v>15.42682425767117</v>
+        <v>15.10597502157363</v>
       </c>
       <c r="D54">
-        <v>6.729224257671179</v>
+        <v>6.729575021573631</v>
       </c>
       <c r="E54">
-        <v>14.6824</v>
+        <v>15.0036</v>
       </c>
       <c r="F54">
-        <v>16.7024</v>
+        <v>17.0236</v>
       </c>
       <c r="G54">
         <v>25.4</v>
@@ -5715,28 +5715,28 @@
         <v>2.46</v>
       </c>
       <c r="M54">
-        <v>1.503216</v>
+        <v>1.532124</v>
       </c>
       <c r="N54">
-        <v>0.9567839999999996</v>
+        <v>0.9278759999999999</v>
       </c>
       <c r="O54">
-        <v>0.2583316799999999</v>
+        <v>0.25052652</v>
       </c>
       <c r="P54">
-        <v>0.6984523199999997</v>
+        <v>0.6773494799999999</v>
       </c>
       <c r="Q54">
-        <v>0.8384523199999998</v>
+        <v>0.8173494800000001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1854924149767041</v>
+        <v>0.1880164851264273</v>
       </c>
       <c r="T54">
-        <v>1.673479136112881</v>
+        <v>1.703716846115614</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.636491362518759</v>
+        <v>1.605614166999538</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1231887480094208</v>
+        <v>0.1231771368300236</v>
       </c>
       <c r="C55">
-        <v>15.10597502157363</v>
+        <v>14.78512582204545</v>
       </c>
       <c r="D55">
-        <v>6.729575021573631</v>
+        <v>6.729925822045448</v>
       </c>
       <c r="E55">
-        <v>15.0036</v>
+        <v>15.3248</v>
       </c>
       <c r="F55">
-        <v>17.0236</v>
+        <v>17.3448</v>
       </c>
       <c r="G55">
         <v>25.4</v>
@@ -5797,28 +5797,28 @@
         <v>2.46</v>
       </c>
       <c r="M55">
-        <v>1.532124</v>
+        <v>1.561032</v>
       </c>
       <c r="N55">
-        <v>0.9278759999999999</v>
+        <v>0.8989679999999998</v>
       </c>
       <c r="O55">
-        <v>0.25052652</v>
+        <v>0.2427213599999999</v>
       </c>
       <c r="P55">
-        <v>0.6773494799999999</v>
+        <v>0.6562466399999998</v>
       </c>
       <c r="Q55">
-        <v>0.8173494800000001</v>
+        <v>0.7962466399999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1880164851264273</v>
+        <v>0.1906502974565731</v>
       </c>
       <c r="T55">
-        <v>1.703716846115614</v>
+        <v>1.735269239161944</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.605614166999538</v>
+        <v>1.575880571314361</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1231771368300236</v>
+        <v>0.1231655256506265</v>
       </c>
       <c r="C56">
-        <v>14.78512582204545</v>
+        <v>14.46427665909234</v>
       </c>
       <c r="D56">
-        <v>6.729925822045448</v>
+        <v>6.73027665909235</v>
       </c>
       <c r="E56">
-        <v>15.3248</v>
+        <v>15.646</v>
       </c>
       <c r="F56">
-        <v>17.3448</v>
+        <v>17.666</v>
       </c>
       <c r="G56">
         <v>25.4</v>
@@ -5879,28 +5879,28 @@
         <v>2.46</v>
       </c>
       <c r="M56">
-        <v>1.561032</v>
+        <v>1.58994</v>
       </c>
       <c r="N56">
-        <v>0.8989679999999998</v>
+        <v>0.8700599999999996</v>
       </c>
       <c r="O56">
-        <v>0.2427213599999999</v>
+        <v>0.2349161999999999</v>
       </c>
       <c r="P56">
-        <v>0.6562466399999998</v>
+        <v>0.6351437999999997</v>
       </c>
       <c r="Q56">
-        <v>0.7962466399999999</v>
+        <v>0.7751437999999998</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1906502974565731</v>
+        <v>0.1934011681125033</v>
       </c>
       <c r="T56">
-        <v>1.735269239161944</v>
+        <v>1.768223960788111</v>
       </c>
       <c r="U56">
         <v>0.09</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.575880571314361</v>
+        <v>1.547228197290464</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1231655256506265</v>
+        <v>0.1231539144712293</v>
       </c>
       <c r="C57">
-        <v>14.46427665909234</v>
+        <v>14.14342753272005</v>
       </c>
       <c r="D57">
-        <v>6.73027665909235</v>
+        <v>6.730627532720056</v>
       </c>
       <c r="E57">
-        <v>15.646</v>
+        <v>15.96720000000001</v>
       </c>
       <c r="F57">
-        <v>17.666</v>
+        <v>17.9872</v>
       </c>
       <c r="G57">
         <v>25.4</v>
@@ -5961,28 +5961,28 @@
         <v>2.46</v>
       </c>
       <c r="M57">
-        <v>1.58994</v>
+        <v>1.618848</v>
       </c>
       <c r="N57">
-        <v>0.8700599999999996</v>
+        <v>0.8411519999999997</v>
       </c>
       <c r="O57">
-        <v>0.2349161999999999</v>
+        <v>0.2271110399999999</v>
       </c>
       <c r="P57">
-        <v>0.6351437999999997</v>
+        <v>0.6140409599999997</v>
       </c>
       <c r="Q57">
-        <v>0.7751437999999998</v>
+        <v>0.7540409599999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1934011681125033</v>
+        <v>0.1962770783437029</v>
       </c>
       <c r="T57">
-        <v>1.768223960788111</v>
+        <v>1.802676624306375</v>
       </c>
       <c r="U57">
         <v>0.09</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.547228197290464</v>
+        <v>1.519599122338848</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1231539144712293</v>
+        <v>0.1497075296704378</v>
       </c>
       <c r="C58">
-        <v>14.14342753272005</v>
+        <v>13.10525334279775</v>
       </c>
       <c r="D58">
-        <v>6.730627532720056</v>
+        <v>6.01365334279776</v>
       </c>
       <c r="E58">
-        <v>15.96720000000001</v>
+        <v>16.28840000000001</v>
       </c>
       <c r="F58">
-        <v>17.9872</v>
+        <v>18.30840000000001</v>
       </c>
       <c r="G58">
         <v>25.4</v>
@@ -6043,45 +6043,45 @@
         <v>2.46</v>
       </c>
       <c r="M58">
-        <v>1.618848</v>
+        <v>2.687673120000001</v>
       </c>
       <c r="N58">
-        <v>0.8411519999999997</v>
+        <v>-0.2276731200000013</v>
       </c>
       <c r="O58">
-        <v>0.2271110399999999</v>
+        <v>-0.06147174240000035</v>
       </c>
       <c r="P58">
-        <v>0.6140409599999997</v>
+        <v>-0.1662013776000009</v>
       </c>
       <c r="Q58">
-        <v>0.7540409599999999</v>
+        <v>-0.0262013776000008</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1962770783437029</v>
+        <v>0.2016517082028484</v>
       </c>
       <c r="T58">
-        <v>1.802676624306375</v>
+        <v>1.867063305108688</v>
       </c>
       <c r="U58">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.27</v>
+        <v>0.2471282668481648</v>
       </c>
       <c r="W58">
-        <v>0.06569999999999999</v>
+        <v>0.1105215704266894</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y58">
-        <v>1.519599122338848</v>
+        <v>0.9152898772154252</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1497075296704378</v>
+        <v>0.1507175296704378</v>
       </c>
       <c r="C59">
-        <v>13.10525334279775</v>
+        <v>12.75978567951188</v>
       </c>
       <c r="D59">
-        <v>6.01365334279776</v>
+        <v>5.989385679511884</v>
       </c>
       <c r="E59">
-        <v>16.28840000000001</v>
+        <v>16.6096</v>
       </c>
       <c r="F59">
-        <v>18.30840000000001</v>
+        <v>18.6296</v>
       </c>
       <c r="G59">
         <v>25.4</v>
@@ -6125,37 +6125,37 @@
         <v>2.46</v>
       </c>
       <c r="M59">
-        <v>2.687673120000001</v>
+        <v>2.734825280000001</v>
       </c>
       <c r="N59">
-        <v>-0.2276731200000013</v>
+        <v>-0.2748252800000008</v>
       </c>
       <c r="O59">
-        <v>-0.06147174240000035</v>
+        <v>-0.07420282560000023</v>
       </c>
       <c r="P59">
-        <v>-0.1662013776000009</v>
+        <v>-0.2006224544000006</v>
       </c>
       <c r="Q59">
-        <v>-0.0262013776000008</v>
+        <v>-0.06062245440000047</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2016517082028484</v>
+        <v>0.2053624631600591</v>
       </c>
       <c r="T59">
-        <v>1.867063305108688</v>
+        <v>1.911517193325562</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.2471282668481648</v>
+        <v>0.2428674346611275</v>
       </c>
       <c r="W59">
-        <v>0.1105215704266894</v>
+        <v>0.1111470605917465</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.9152898772154252</v>
+        <v>0.8995090172634352</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1507175296704378</v>
+        <v>0.1517275296704378</v>
       </c>
       <c r="C60">
-        <v>12.75978567951188</v>
+        <v>12.41451308982196</v>
       </c>
       <c r="D60">
-        <v>5.989385679511884</v>
+        <v>5.965313089821961</v>
       </c>
       <c r="E60">
-        <v>16.6096</v>
+        <v>16.9308</v>
       </c>
       <c r="F60">
-        <v>18.6296</v>
+        <v>18.9508</v>
       </c>
       <c r="G60">
         <v>25.4</v>
@@ -6207,37 +6207,37 @@
         <v>2.46</v>
       </c>
       <c r="M60">
-        <v>2.73482528</v>
+        <v>2.78197744</v>
       </c>
       <c r="N60">
-        <v>-0.2748252800000004</v>
+        <v>-0.3219774400000004</v>
       </c>
       <c r="O60">
-        <v>-0.07420282560000011</v>
+        <v>-0.08693390880000011</v>
       </c>
       <c r="P60">
-        <v>-0.2006224544000003</v>
+        <v>-0.2350435312000003</v>
       </c>
       <c r="Q60">
-        <v>-0.06062245440000016</v>
+        <v>-0.09504353120000014</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2053624631600591</v>
+        <v>0.2092542305542068</v>
       </c>
       <c r="T60">
-        <v>1.911517193325561</v>
+        <v>1.958139563894477</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.2428674346611276</v>
+        <v>0.2387510374634813</v>
       </c>
       <c r="W60">
-        <v>0.1111470605917465</v>
+        <v>0.111751347700361</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8995090172634355</v>
+        <v>0.8842631017165975</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1517275296704378</v>
+        <v>0.1527375296704377</v>
       </c>
       <c r="C61">
-        <v>12.41451308982196</v>
+        <v>12.06943323101946</v>
       </c>
       <c r="D61">
-        <v>5.965313089821961</v>
+        <v>5.941433231019468</v>
       </c>
       <c r="E61">
-        <v>16.9308</v>
+        <v>17.252</v>
       </c>
       <c r="F61">
-        <v>18.9508</v>
+        <v>19.272</v>
       </c>
       <c r="G61">
         <v>25.4</v>
@@ -6289,37 +6289,37 @@
         <v>2.46</v>
       </c>
       <c r="M61">
-        <v>2.78197744</v>
+        <v>2.8291296</v>
       </c>
       <c r="N61">
-        <v>-0.3219774400000004</v>
+        <v>-0.3691296000000004</v>
       </c>
       <c r="O61">
-        <v>-0.08693390880000011</v>
+        <v>-0.09966499200000012</v>
       </c>
       <c r="P61">
-        <v>-0.2350435312000003</v>
+        <v>-0.2694646080000003</v>
       </c>
       <c r="Q61">
-        <v>-0.09504353120000014</v>
+        <v>-0.1294646080000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2092542305542068</v>
+        <v>0.213340586318062</v>
       </c>
       <c r="T61">
-        <v>1.958139563894477</v>
+        <v>2.007093052991839</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.2387510374634813</v>
+        <v>0.2347718535057567</v>
       </c>
       <c r="W61">
-        <v>0.111751347700361</v>
+        <v>0.1123354919053549</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8842631017165975</v>
+        <v>0.8695253833546542</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1527375296704377</v>
+        <v>0.1537475296704378</v>
       </c>
       <c r="C62">
-        <v>12.06943323101946</v>
+        <v>11.72454379775888</v>
       </c>
       <c r="D62">
-        <v>5.941433231019468</v>
+        <v>5.917743797758884</v>
       </c>
       <c r="E62">
-        <v>17.252</v>
+        <v>17.5732</v>
       </c>
       <c r="F62">
-        <v>19.272</v>
+        <v>19.5932</v>
       </c>
       <c r="G62">
         <v>25.4</v>
@@ -6371,37 +6371,37 @@
         <v>2.46</v>
       </c>
       <c r="M62">
-        <v>2.8291296</v>
+        <v>2.876281760000001</v>
       </c>
       <c r="N62">
-        <v>-0.3691296000000004</v>
+        <v>-0.4162817600000008</v>
       </c>
       <c r="O62">
-        <v>-0.09966499200000012</v>
+        <v>-0.1123960752000002</v>
       </c>
       <c r="P62">
-        <v>-0.2694646080000003</v>
+        <v>-0.3038856848000006</v>
       </c>
       <c r="Q62">
-        <v>-0.1294646080000001</v>
+        <v>-0.1638856848000005</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.213340586318062</v>
+        <v>0.2176364987877559</v>
       </c>
       <c r="T62">
-        <v>2.007093052991839</v>
+        <v>2.058556977427528</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.2347718535057567</v>
+        <v>0.2309231345958262</v>
       </c>
       <c r="W62">
-        <v>0.1123354919053549</v>
+        <v>0.1129004838413327</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8695253833546542</v>
+        <v>0.8552708688734303</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1537475296704378</v>
+        <v>0.1547575296704378</v>
       </c>
       <c r="C63">
-        <v>11.72454379775888</v>
+        <v>11.37984252131578</v>
       </c>
       <c r="D63">
-        <v>5.917743797758884</v>
+        <v>5.894242521315786</v>
       </c>
       <c r="E63">
-        <v>17.5732</v>
+        <v>17.8944</v>
       </c>
       <c r="F63">
-        <v>19.5932</v>
+        <v>19.9144</v>
       </c>
       <c r="G63">
         <v>25.4</v>
@@ -6453,37 +6453,37 @@
         <v>2.46</v>
       </c>
       <c r="M63">
-        <v>2.876281760000001</v>
+        <v>2.923433920000001</v>
       </c>
       <c r="N63">
-        <v>-0.4162817600000008</v>
+        <v>-0.4634339200000008</v>
       </c>
       <c r="O63">
-        <v>-0.1123960752000002</v>
+        <v>-0.1251271584000002</v>
       </c>
       <c r="P63">
-        <v>-0.3038856848000006</v>
+        <v>-0.3383067616000006</v>
       </c>
       <c r="Q63">
-        <v>-0.1638856848000005</v>
+        <v>-0.1983067616000005</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2176364987877559</v>
+        <v>0.2221585119137496</v>
       </c>
       <c r="T63">
-        <v>2.058556977427528</v>
+        <v>2.112729529465095</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.2309231345958262</v>
+        <v>0.2271985679087967</v>
       </c>
       <c r="W63">
-        <v>0.1129004838413327</v>
+        <v>0.1134472502309887</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8552708688734303</v>
+        <v>0.8414761774399879</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1547575296704378</v>
+        <v>0.1557675296704378</v>
       </c>
       <c r="C64">
-        <v>11.37984252131578</v>
+        <v>11.03532716886254</v>
       </c>
       <c r="D64">
-        <v>5.894242521315786</v>
+        <v>5.870927168862544</v>
       </c>
       <c r="E64">
-        <v>17.8944</v>
+        <v>18.2156</v>
       </c>
       <c r="F64">
-        <v>19.9144</v>
+        <v>20.2356</v>
       </c>
       <c r="G64">
         <v>25.4</v>
@@ -6535,37 +6535,37 @@
         <v>2.46</v>
       </c>
       <c r="M64">
-        <v>2.923433920000001</v>
+        <v>2.97058608</v>
       </c>
       <c r="N64">
-        <v>-0.4634339200000008</v>
+        <v>-0.5105860800000004</v>
       </c>
       <c r="O64">
-        <v>-0.1251271584000002</v>
+        <v>-0.1378582416000001</v>
       </c>
       <c r="P64">
-        <v>-0.3383067616000006</v>
+        <v>-0.3727278384000002</v>
       </c>
       <c r="Q64">
-        <v>-0.1983067616000005</v>
+        <v>-0.2327278384000001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2221585119137496</v>
+        <v>0.2269249581816887</v>
       </c>
       <c r="T64">
-        <v>2.112729529465095</v>
+        <v>2.169830327558746</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.2271985679087967</v>
+        <v>0.223592241434054</v>
       </c>
       <c r="W64">
-        <v>0.1134472502309887</v>
+        <v>0.1139766589574809</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8414761774399879</v>
+        <v>0.8281194127187184</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1557675296704378</v>
+        <v>0.1567775296704378</v>
       </c>
       <c r="C65">
-        <v>11.03532716886254</v>
+        <v>10.69099554276115</v>
       </c>
       <c r="D65">
-        <v>5.870927168862544</v>
+        <v>5.847795542761159</v>
       </c>
       <c r="E65">
-        <v>18.2156</v>
+        <v>18.5368</v>
       </c>
       <c r="F65">
-        <v>20.2356</v>
+        <v>20.5568</v>
       </c>
       <c r="G65">
         <v>25.4</v>
@@ -6617,37 +6617,37 @@
         <v>2.46</v>
       </c>
       <c r="M65">
-        <v>2.97058608</v>
+        <v>3.017738240000001</v>
       </c>
       <c r="N65">
-        <v>-0.5105860800000004</v>
+        <v>-0.5577382400000008</v>
       </c>
       <c r="O65">
-        <v>-0.1378582416000001</v>
+        <v>-0.1505893248000002</v>
       </c>
       <c r="P65">
-        <v>-0.3727278384000002</v>
+        <v>-0.4071489152000006</v>
       </c>
       <c r="Q65">
-        <v>-0.2327278384000001</v>
+        <v>-0.2671489152000005</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2269249581816887</v>
+        <v>0.2319562070200689</v>
       </c>
       <c r="T65">
-        <v>2.169830327558746</v>
+        <v>2.230103392213155</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.223592241434054</v>
+        <v>0.2200986126616468</v>
       </c>
       <c r="W65">
-        <v>0.1139766589574809</v>
+        <v>0.1144895236612702</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8281194127187184</v>
+        <v>0.8151800468949882</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1567775296704378</v>
+        <v>0.1577875296704378</v>
       </c>
       <c r="C66">
-        <v>10.69099554276115</v>
+        <v>10.34684547987273</v>
       </c>
       <c r="D66">
-        <v>5.847795542761159</v>
+        <v>5.824845479872732</v>
       </c>
       <c r="E66">
-        <v>18.5368</v>
+        <v>18.858</v>
       </c>
       <c r="F66">
-        <v>20.5568</v>
+        <v>20.878</v>
       </c>
       <c r="G66">
         <v>25.4</v>
@@ -6699,37 +6699,37 @@
         <v>2.46</v>
       </c>
       <c r="M66">
-        <v>3.017738240000001</v>
+        <v>3.064890400000001</v>
       </c>
       <c r="N66">
-        <v>-0.5577382400000008</v>
+        <v>-0.6048904000000008</v>
       </c>
       <c r="O66">
-        <v>-0.1505893248000002</v>
+        <v>-0.1633204080000002</v>
       </c>
       <c r="P66">
-        <v>-0.4071489152000006</v>
+        <v>-0.4415699920000006</v>
       </c>
       <c r="Q66">
-        <v>-0.2671489152000005</v>
+        <v>-0.3015699920000005</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2319562070200689</v>
+        <v>0.2372749557920709</v>
       </c>
       <c r="T66">
-        <v>2.230103392213155</v>
+        <v>2.293820631990674</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.2200986126616468</v>
+        <v>0.21671248015916</v>
       </c>
       <c r="W66">
-        <v>0.1144895236612702</v>
+        <v>0.1149866079126353</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8151800468949882</v>
+        <v>0.8026388154042962</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1577875296704378</v>
+        <v>0.1973924446279741</v>
       </c>
       <c r="C67">
-        <v>10.34684547987273</v>
+        <v>9.248793621803394</v>
       </c>
       <c r="D67">
-        <v>5.824845479872732</v>
+        <v>5.047993621803399</v>
       </c>
       <c r="E67">
-        <v>18.858</v>
+        <v>19.17920000000001</v>
       </c>
       <c r="F67">
-        <v>20.878</v>
+        <v>21.1992</v>
       </c>
       <c r="G67">
         <v>25.4</v>
@@ -6781,45 +6781,45 @@
         <v>2.46</v>
       </c>
       <c r="M67">
-        <v>3.064890400000001</v>
+        <v>4.256799360000001</v>
       </c>
       <c r="N67">
-        <v>-0.6048904000000008</v>
+        <v>-1.796799360000001</v>
       </c>
       <c r="O67">
-        <v>-0.1633204080000002</v>
+        <v>-0.4851358272000004</v>
       </c>
       <c r="P67">
-        <v>-0.4415699920000006</v>
+        <v>-1.311663532800001</v>
       </c>
       <c r="Q67">
-        <v>-0.3015699920000005</v>
+        <v>-1.171663532800001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2372749557920709</v>
+        <v>0.2515974984845915</v>
       </c>
       <c r="T67">
-        <v>2.293820631990674</v>
+        <v>2.465401002879218</v>
       </c>
       <c r="U67">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.21671248015916</v>
+        <v>0.156032724079342</v>
       </c>
       <c r="W67">
-        <v>0.1149866079126353</v>
+        <v>0.1694686290048681</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y67">
-        <v>0.8026388154042962</v>
+        <v>0.5778989780716373</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1973924446279741</v>
+        <v>0.1989424446279741</v>
       </c>
       <c r="C68">
-        <v>9.248793621803394</v>
+        <v>8.901381977453159</v>
       </c>
       <c r="D68">
-        <v>5.047993621803399</v>
+        <v>5.021781977453165</v>
       </c>
       <c r="E68">
-        <v>19.17920000000001</v>
+        <v>19.50040000000001</v>
       </c>
       <c r="F68">
-        <v>21.1992</v>
+        <v>21.52040000000001</v>
       </c>
       <c r="G68">
         <v>25.4</v>
@@ -6863,37 +6863,37 @@
         <v>2.46</v>
       </c>
       <c r="M68">
-        <v>4.256799360000001</v>
+        <v>4.321296320000001</v>
       </c>
       <c r="N68">
-        <v>-1.796799360000001</v>
+        <v>-1.861296320000001</v>
       </c>
       <c r="O68">
-        <v>-0.4851358272000004</v>
+        <v>-0.5025500064000002</v>
       </c>
       <c r="P68">
-        <v>-1.311663532800001</v>
+        <v>-1.358746313600001</v>
       </c>
       <c r="Q68">
-        <v>-1.171663532800001</v>
+        <v>-1.218746313600001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2515974984845915</v>
+        <v>0.2578337863174579</v>
       </c>
       <c r="T68">
-        <v>2.465401002879218</v>
+        <v>2.540110124178588</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.156032724079342</v>
+        <v>0.1537038774512922</v>
       </c>
       <c r="W68">
-        <v>0.1694686290048681</v>
+        <v>0.1699362614077805</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5778989780716373</v>
+        <v>0.5692736201899711</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1989424446279741</v>
+        <v>0.2004924446279741</v>
       </c>
       <c r="C69">
-        <v>8.901381977453159</v>
+        <v>8.554241134248525</v>
       </c>
       <c r="D69">
-        <v>5.021781977453165</v>
+        <v>4.995841134248531</v>
       </c>
       <c r="E69">
-        <v>19.50040000000001</v>
+        <v>19.8216</v>
       </c>
       <c r="F69">
-        <v>21.52040000000001</v>
+        <v>21.8416</v>
       </c>
       <c r="G69">
         <v>25.4</v>
@@ -6945,37 +6945,37 @@
         <v>2.46</v>
       </c>
       <c r="M69">
-        <v>4.321296320000001</v>
+        <v>4.385793280000001</v>
       </c>
       <c r="N69">
-        <v>-1.861296320000001</v>
+        <v>-1.925793280000001</v>
       </c>
       <c r="O69">
-        <v>-0.5025500064000002</v>
+        <v>-0.5199641856000002</v>
       </c>
       <c r="P69">
-        <v>-1.358746313600001</v>
+        <v>-1.4058290944</v>
       </c>
       <c r="Q69">
-        <v>-1.218746313600001</v>
+        <v>-1.2658290944</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2578337863174579</v>
+        <v>0.2644598421398785</v>
       </c>
       <c r="T69">
-        <v>2.540110124178588</v>
+        <v>2.619488565559169</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1537038774512922</v>
+        <v>0.1514435263123026</v>
       </c>
       <c r="W69">
-        <v>0.1699362614077805</v>
+        <v>0.1703901399164896</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5692736201899711</v>
+        <v>0.5609019493048244</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2004924446279741</v>
+        <v>0.202042444627974</v>
       </c>
       <c r="C70">
-        <v>8.554241134248525</v>
+        <v>8.207366917152367</v>
       </c>
       <c r="D70">
-        <v>4.995841134248531</v>
+        <v>4.970166917152373</v>
       </c>
       <c r="E70">
-        <v>19.8216</v>
+        <v>20.1428</v>
       </c>
       <c r="F70">
-        <v>21.8416</v>
+        <v>22.1628</v>
       </c>
       <c r="G70">
         <v>25.4</v>
@@ -7027,37 +7027,37 @@
         <v>2.46</v>
       </c>
       <c r="M70">
-        <v>4.385793280000001</v>
+        <v>4.450290240000001</v>
       </c>
       <c r="N70">
-        <v>-1.925793280000001</v>
+        <v>-1.990290240000001</v>
       </c>
       <c r="O70">
-        <v>-0.5199641856000002</v>
+        <v>-0.5373783648000003</v>
       </c>
       <c r="P70">
-        <v>-1.4058290944</v>
+        <v>-1.452911875200001</v>
       </c>
       <c r="Q70">
-        <v>-1.2658290944</v>
+        <v>-1.312911875200001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2644598421398785</v>
+        <v>0.2715133854347133</v>
       </c>
       <c r="T70">
-        <v>2.619488565559169</v>
+        <v>2.703988196706239</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1514435263123026</v>
+        <v>0.1492486925976315</v>
       </c>
       <c r="W70">
-        <v>0.1703901399164896</v>
+        <v>0.1708308625263956</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5609019493048244</v>
+        <v>0.5527729355467834</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.202042444627974</v>
+        <v>0.203592444627974</v>
       </c>
       <c r="C71">
-        <v>8.207366917152367</v>
+        <v>7.860755236512787</v>
       </c>
       <c r="D71">
-        <v>4.970166917152373</v>
+        <v>4.944755236512793</v>
       </c>
       <c r="E71">
-        <v>20.1428</v>
+        <v>20.46400000000001</v>
       </c>
       <c r="F71">
-        <v>22.1628</v>
+        <v>22.48400000000001</v>
       </c>
       <c r="G71">
         <v>25.4</v>
@@ -7109,37 +7109,37 @@
         <v>2.46</v>
       </c>
       <c r="M71">
-        <v>4.450290240000001</v>
+        <v>4.514787200000002</v>
       </c>
       <c r="N71">
-        <v>-1.990290240000001</v>
+        <v>-2.054787200000002</v>
       </c>
       <c r="O71">
-        <v>-0.5373783648000003</v>
+        <v>-0.5547925440000004</v>
       </c>
       <c r="P71">
-        <v>-1.452911875200001</v>
+        <v>-1.499994656000001</v>
       </c>
       <c r="Q71">
-        <v>-1.312911875200001</v>
+        <v>-1.359994656000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2715133854347133</v>
+        <v>0.2790371649492037</v>
       </c>
       <c r="T71">
-        <v>2.703988196706239</v>
+        <v>2.794121136596447</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1492486925976315</v>
+        <v>0.1471165684176653</v>
       </c>
       <c r="W71">
-        <v>0.1708308625263956</v>
+        <v>0.1712589930617328</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5527729355467834</v>
+        <v>0.5448761793246865</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.203592444627974</v>
+        <v>0.2051424446279741</v>
       </c>
       <c r="C72">
-        <v>7.860755236512787</v>
+        <v>7.514402085891415</v>
       </c>
       <c r="D72">
-        <v>4.944755236512793</v>
+        <v>4.919602085891423</v>
       </c>
       <c r="E72">
-        <v>20.46400000000001</v>
+        <v>20.78520000000001</v>
       </c>
       <c r="F72">
-        <v>22.48400000000001</v>
+        <v>22.80520000000001</v>
       </c>
       <c r="G72">
         <v>25.4</v>
@@ -7191,37 +7191,37 @@
         <v>2.46</v>
       </c>
       <c r="M72">
-        <v>4.514787200000002</v>
+        <v>4.579284160000001</v>
       </c>
       <c r="N72">
-        <v>-2.054787200000002</v>
+        <v>-2.119284160000001</v>
       </c>
       <c r="O72">
-        <v>-0.5547925440000004</v>
+        <v>-0.5722067232000003</v>
       </c>
       <c r="P72">
-        <v>-1.499994656000001</v>
+        <v>-1.547077436800001</v>
       </c>
       <c r="Q72">
-        <v>-1.359994656000001</v>
+        <v>-1.407077436800001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2790371649492037</v>
+        <v>0.2870798258095211</v>
       </c>
       <c r="T72">
-        <v>2.794121136596447</v>
+        <v>2.89047014130667</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1471165684176653</v>
+        <v>0.1450445040737546</v>
       </c>
       <c r="W72">
-        <v>0.1712589930617328</v>
+        <v>0.1716750635819901</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5448761793246865</v>
+        <v>0.5372018669398317</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.205142444627974</v>
+        <v>0.206692444627974</v>
       </c>
       <c r="C73">
-        <v>7.514402085891419</v>
+        <v>7.168303539957662</v>
       </c>
       <c r="D73">
-        <v>4.919602085891424</v>
+        <v>4.894703539957666</v>
       </c>
       <c r="E73">
-        <v>20.7852</v>
+        <v>21.1064</v>
       </c>
       <c r="F73">
-        <v>22.8052</v>
+        <v>23.1264</v>
       </c>
       <c r="G73">
         <v>25.4</v>
@@ -7273,37 +7273,37 @@
         <v>2.46</v>
       </c>
       <c r="M73">
-        <v>4.57928416</v>
+        <v>4.643781120000001</v>
       </c>
       <c r="N73">
-        <v>-2.11928416</v>
+        <v>-2.183781120000001</v>
       </c>
       <c r="O73">
-        <v>-0.5722067232000001</v>
+        <v>-0.5896209024000002</v>
       </c>
       <c r="P73">
-        <v>-1.5470774368</v>
+        <v>-1.594160217600001</v>
       </c>
       <c r="Q73">
-        <v>-1.4070774368</v>
+        <v>-1.454160217600001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.287079825809521</v>
+        <v>0.2956969624455754</v>
       </c>
       <c r="T73">
-        <v>2.890470141306669</v>
+        <v>2.993701217781907</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1450445040737546</v>
+        <v>0.1430299970727302</v>
       </c>
       <c r="W73">
-        <v>0.1716750635819901</v>
+        <v>0.1720795765877958</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.537201866939832</v>
+        <v>0.5297407298990009</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.206692444627974</v>
+        <v>0.2082424446279741</v>
       </c>
       <c r="C74">
-        <v>7.168303539957662</v>
+        <v>6.822455752446555</v>
       </c>
       <c r="D74">
-        <v>4.894703539957666</v>
+        <v>4.870055752446558</v>
       </c>
       <c r="E74">
-        <v>21.1064</v>
+        <v>21.4276</v>
       </c>
       <c r="F74">
-        <v>23.1264</v>
+        <v>23.4476</v>
       </c>
       <c r="G74">
         <v>25.4</v>
@@ -7355,37 +7355,37 @@
         <v>2.46</v>
       </c>
       <c r="M74">
-        <v>4.643781120000001</v>
+        <v>4.70827808</v>
       </c>
       <c r="N74">
-        <v>-2.183781120000001</v>
+        <v>-2.24827808</v>
       </c>
       <c r="O74">
-        <v>-0.5896209024000002</v>
+        <v>-0.6070350816000002</v>
       </c>
       <c r="P74">
-        <v>-1.594160217600001</v>
+        <v>-1.6412429984</v>
       </c>
       <c r="Q74">
-        <v>-1.454160217600001</v>
+        <v>-1.5012429984</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2956969624455754</v>
+        <v>0.3049524054991152</v>
       </c>
       <c r="T74">
-        <v>2.993701217781907</v>
+        <v>3.104579040662718</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1430299970727302</v>
+        <v>0.1410706820443367</v>
       </c>
       <c r="W74">
-        <v>0.1720795765877958</v>
+        <v>0.1724730070454972</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5297407298990009</v>
+        <v>0.5224840075716173</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2082424446279741</v>
+        <v>0.2097924446279741</v>
       </c>
       <c r="C75">
-        <v>6.822455752446555</v>
+        <v>6.476854954178034</v>
       </c>
       <c r="D75">
-        <v>4.870055752446558</v>
+        <v>4.845654954178036</v>
       </c>
       <c r="E75">
-        <v>21.4276</v>
+        <v>21.7488</v>
       </c>
       <c r="F75">
-        <v>23.4476</v>
+        <v>23.7688</v>
       </c>
       <c r="G75">
         <v>25.4</v>
@@ -7437,37 +7437,37 @@
         <v>2.46</v>
       </c>
       <c r="M75">
-        <v>4.70827808</v>
+        <v>4.772775040000001</v>
       </c>
       <c r="N75">
-        <v>-2.24827808</v>
+        <v>-2.312775040000001</v>
       </c>
       <c r="O75">
-        <v>-0.6070350816000002</v>
+        <v>-0.6244492608000003</v>
       </c>
       <c r="P75">
-        <v>-1.6412429984</v>
+        <v>-1.688325779200001</v>
       </c>
       <c r="Q75">
-        <v>-1.5012429984</v>
+        <v>-1.5483257792</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3049524054991152</v>
+        <v>0.3149198057106197</v>
       </c>
       <c r="T75">
-        <v>3.104579040662718</v>
+        <v>3.223985926842054</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1410706820443367</v>
+        <v>0.1391643214761699</v>
       </c>
       <c r="W75">
-        <v>0.1724730070454972</v>
+        <v>0.1728558042475851</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5224840075716173</v>
+        <v>0.5154234128747035</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2097924446279741</v>
+        <v>0.211342444627974</v>
       </c>
       <c r="C76">
-        <v>6.476854954178034</v>
+        <v>6.131497451135434</v>
       </c>
       <c r="D76">
-        <v>4.845654954178036</v>
+        <v>4.821497451135439</v>
       </c>
       <c r="E76">
-        <v>21.7488</v>
+        <v>22.07</v>
       </c>
       <c r="F76">
-        <v>23.7688</v>
+        <v>24.09</v>
       </c>
       <c r="G76">
         <v>25.4</v>
@@ -7519,37 +7519,37 @@
         <v>2.46</v>
       </c>
       <c r="M76">
-        <v>4.772775040000001</v>
+        <v>4.837272</v>
       </c>
       <c r="N76">
-        <v>-2.312775040000001</v>
+        <v>-2.377272</v>
       </c>
       <c r="O76">
-        <v>-0.6244492608000003</v>
+        <v>-0.6418634400000002</v>
       </c>
       <c r="P76">
-        <v>-1.688325779200001</v>
+        <v>-1.73540856</v>
       </c>
       <c r="Q76">
-        <v>-1.5483257792</v>
+        <v>-1.59540856</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3149198057106197</v>
+        <v>0.3256845979390444</v>
       </c>
       <c r="T76">
-        <v>3.223985926842054</v>
+        <v>3.352945363915736</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1391643214761699</v>
+        <v>0.1373087971898211</v>
       </c>
       <c r="W76">
-        <v>0.1728558042475851</v>
+        <v>0.1732283935242839</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5154234128747035</v>
+        <v>0.5085511007030408</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.211342444627974</v>
+        <v>0.212892444627974</v>
       </c>
       <c r="C77">
-        <v>6.131497451135434</v>
+        <v>5.786379622601199</v>
       </c>
       <c r="D77">
-        <v>4.821497451135439</v>
+        <v>4.797579622601205</v>
       </c>
       <c r="E77">
-        <v>22.07</v>
+        <v>22.3912</v>
       </c>
       <c r="F77">
-        <v>24.09</v>
+        <v>24.4112</v>
       </c>
       <c r="G77">
         <v>25.4</v>
@@ -7601,37 +7601,37 @@
         <v>2.46</v>
       </c>
       <c r="M77">
-        <v>4.837272</v>
+        <v>4.901768960000001</v>
       </c>
       <c r="N77">
-        <v>-2.377272</v>
+        <v>-2.441768960000001</v>
       </c>
       <c r="O77">
-        <v>-0.6418634400000002</v>
+        <v>-0.6592776192000003</v>
       </c>
       <c r="P77">
-        <v>-1.73540856</v>
+        <v>-1.782491340800001</v>
       </c>
       <c r="Q77">
-        <v>-1.59540856</v>
+        <v>-1.642491340800001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3256845979390444</v>
+        <v>0.3373464561865046</v>
       </c>
       <c r="T77">
-        <v>3.352945363915736</v>
+        <v>3.492651420745558</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1373087971898211</v>
+        <v>0.135502102489955</v>
       </c>
       <c r="W77">
-        <v>0.1732283935242839</v>
+        <v>0.173591177820017</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5085511007030408</v>
+        <v>0.5018596388516849</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.212892444627974</v>
+        <v>0.2425847885047546</v>
       </c>
       <c r="C78">
-        <v>5.786379622601199</v>
+        <v>5.04883834544442</v>
       </c>
       <c r="D78">
-        <v>4.797579622601205</v>
+        <v>4.381238345444427</v>
       </c>
       <c r="E78">
-        <v>22.3912</v>
+        <v>22.71240000000001</v>
       </c>
       <c r="F78">
-        <v>24.4112</v>
+        <v>24.73240000000001</v>
       </c>
       <c r="G78">
         <v>25.4</v>
@@ -7683,45 +7683,45 @@
         <v>2.46</v>
       </c>
       <c r="M78">
-        <v>4.901768960000001</v>
+        <v>5.831899920000001</v>
       </c>
       <c r="N78">
-        <v>-2.441768960000001</v>
+        <v>-3.371899920000001</v>
       </c>
       <c r="O78">
-        <v>-0.6592776192000003</v>
+        <v>-0.9104129784000005</v>
       </c>
       <c r="P78">
-        <v>-1.782491340800001</v>
+        <v>-2.461486941600001</v>
       </c>
       <c r="Q78">
-        <v>-1.642491340800001</v>
+        <v>-2.321486941600001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3373464561865046</v>
+        <v>0.3552064928762679</v>
       </c>
       <c r="T78">
-        <v>3.492651420745558</v>
+        <v>3.706610058195657</v>
       </c>
       <c r="U78">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.135502102489955</v>
+        <v>0.1138908433120025</v>
       </c>
       <c r="W78">
-        <v>0.173591177820017</v>
+        <v>0.2089445391470298</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y78">
-        <v>0.5018596388516849</v>
+        <v>0.4218179381926018</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2425847885047546</v>
+        <v>0.2444847885047546</v>
       </c>
       <c r="C79">
-        <v>5.04883834544442</v>
+        <v>4.703443198498903</v>
       </c>
       <c r="D79">
-        <v>4.381238345444427</v>
+        <v>4.357043198498906</v>
       </c>
       <c r="E79">
-        <v>22.71240000000001</v>
+        <v>23.0336</v>
       </c>
       <c r="F79">
-        <v>24.73240000000001</v>
+        <v>25.0536</v>
       </c>
       <c r="G79">
         <v>25.4</v>
@@ -7765,37 +7765,37 @@
         <v>2.46</v>
       </c>
       <c r="M79">
-        <v>5.831899920000001</v>
+        <v>5.907638880000001</v>
       </c>
       <c r="N79">
-        <v>-3.371899920000001</v>
+        <v>-3.447638880000001</v>
       </c>
       <c r="O79">
-        <v>-0.9104129784000005</v>
+        <v>-0.9308624976000004</v>
       </c>
       <c r="P79">
-        <v>-2.461486941600001</v>
+        <v>-2.516776382400001</v>
       </c>
       <c r="Q79">
-        <v>-2.321486941600001</v>
+        <v>-2.376776382400001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3552064928762679</v>
+        <v>0.3692704243706437</v>
       </c>
       <c r="T79">
-        <v>3.706610058195657</v>
+        <v>3.875092333568186</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.1138908433120025</v>
+        <v>0.112430704295182</v>
       </c>
       <c r="W79">
-        <v>0.2089445391470298</v>
+        <v>0.2092888399271961</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4218179381926018</v>
+        <v>0.4164100159080812</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2444847885047546</v>
+        <v>0.2463847885047546</v>
       </c>
       <c r="C80">
-        <v>4.703443198498903</v>
+        <v>4.358313816607705</v>
       </c>
       <c r="D80">
-        <v>4.357043198498906</v>
+        <v>4.333113816607709</v>
       </c>
       <c r="E80">
-        <v>23.0336</v>
+        <v>23.3548</v>
       </c>
       <c r="F80">
-        <v>25.0536</v>
+        <v>25.3748</v>
       </c>
       <c r="G80">
         <v>25.4</v>
@@ -7847,37 +7847,37 @@
         <v>2.46</v>
       </c>
       <c r="M80">
-        <v>5.907638880000001</v>
+        <v>5.983377840000001</v>
       </c>
       <c r="N80">
-        <v>-3.447638880000001</v>
+        <v>-3.523377840000001</v>
       </c>
       <c r="O80">
-        <v>-0.9308624976000004</v>
+        <v>-0.9513120168000003</v>
       </c>
       <c r="P80">
-        <v>-2.516776382400001</v>
+        <v>-2.572065823200001</v>
       </c>
       <c r="Q80">
-        <v>-2.376776382400001</v>
+        <v>-2.432065823200001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3692704243706437</v>
+        <v>0.3846737779121029</v>
       </c>
       <c r="T80">
-        <v>3.875092333568186</v>
+        <v>4.059620539928577</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.112430704295182</v>
+        <v>0.111007530823091</v>
       </c>
       <c r="W80">
-        <v>0.2092888399271961</v>
+        <v>0.2096244242319152</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4164100159080812</v>
+        <v>0.4111390030484853</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2463847885047546</v>
+        <v>0.2482847885047546</v>
       </c>
       <c r="C81">
-        <v>4.358313816607705</v>
+        <v>4.013445844851901</v>
       </c>
       <c r="D81">
-        <v>4.333113816607709</v>
+        <v>4.309445844851906</v>
       </c>
       <c r="E81">
-        <v>23.3548</v>
+        <v>23.67600000000001</v>
       </c>
       <c r="F81">
-        <v>25.3748</v>
+        <v>25.69600000000001</v>
       </c>
       <c r="G81">
         <v>25.4</v>
@@ -7929,37 +7929,37 @@
         <v>2.46</v>
       </c>
       <c r="M81">
-        <v>5.983377840000001</v>
+        <v>6.059116800000002</v>
       </c>
       <c r="N81">
-        <v>-3.523377840000001</v>
+        <v>-3.599116800000002</v>
       </c>
       <c r="O81">
-        <v>-0.9513120168000003</v>
+        <v>-0.9717615360000006</v>
       </c>
       <c r="P81">
-        <v>-2.572065823200001</v>
+        <v>-2.627355264000001</v>
       </c>
       <c r="Q81">
-        <v>-2.432065823200001</v>
+        <v>-2.487355264000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3846737779121029</v>
+        <v>0.4016174668077082</v>
       </c>
       <c r="T81">
-        <v>4.059620539928577</v>
+        <v>4.262601566925007</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.111007530823091</v>
+        <v>0.1096199366878024</v>
       </c>
       <c r="W81">
-        <v>0.2096244242319152</v>
+        <v>0.2099516189290162</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4111390030484853</v>
+        <v>0.4059997655103792</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2482847885047546</v>
+        <v>0.2501847885047546</v>
       </c>
       <c r="C82">
-        <v>4.013445844851901</v>
+        <v>3.668835022943963</v>
       </c>
       <c r="D82">
-        <v>4.309445844851906</v>
+        <v>4.286035022943969</v>
       </c>
       <c r="E82">
-        <v>23.67600000000001</v>
+        <v>23.99720000000001</v>
       </c>
       <c r="F82">
-        <v>25.69600000000001</v>
+        <v>26.01720000000001</v>
       </c>
       <c r="G82">
         <v>25.4</v>
@@ -8011,37 +8011,37 @@
         <v>2.46</v>
       </c>
       <c r="M82">
-        <v>6.059116800000002</v>
+        <v>6.134855760000002</v>
       </c>
       <c r="N82">
-        <v>-3.599116800000002</v>
+        <v>-3.674855760000002</v>
       </c>
       <c r="O82">
-        <v>-0.9717615360000006</v>
+        <v>-0.9922110552000005</v>
       </c>
       <c r="P82">
-        <v>-2.627355264000001</v>
+        <v>-2.682644704800001</v>
       </c>
       <c r="Q82">
-        <v>-2.487355264000001</v>
+        <v>-2.542644704800001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4016174668077082</v>
+        <v>0.4203447019028507</v>
       </c>
       <c r="T82">
-        <v>4.262601566925007</v>
+        <v>4.486949017815796</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.1096199366878024</v>
+        <v>0.1082666041361011</v>
       </c>
       <c r="W82">
-        <v>0.2099516189290162</v>
+        <v>0.2102707347447074</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4059997655103792</v>
+        <v>0.4009874227263005</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2501847885047546</v>
+        <v>0.2520847885047546</v>
       </c>
       <c r="C83">
-        <v>3.668835022943963</v>
+        <v>3.324477182671263</v>
       </c>
       <c r="D83">
-        <v>4.286035022943969</v>
+        <v>4.262877182671271</v>
       </c>
       <c r="E83">
-        <v>23.99720000000001</v>
+        <v>24.31840000000001</v>
       </c>
       <c r="F83">
-        <v>26.01720000000001</v>
+        <v>26.33840000000001</v>
       </c>
       <c r="G83">
         <v>25.4</v>
@@ -8093,37 +8093,37 @@
         <v>2.46</v>
       </c>
       <c r="M83">
-        <v>6.134855760000002</v>
+        <v>6.210594720000002</v>
       </c>
       <c r="N83">
-        <v>-3.674855760000002</v>
+        <v>-3.750594720000002</v>
       </c>
       <c r="O83">
-        <v>-0.9922110552000005</v>
+        <v>-1.012660574400001</v>
       </c>
       <c r="P83">
-        <v>-2.682644704800001</v>
+        <v>-2.737934145600001</v>
       </c>
       <c r="Q83">
-        <v>-2.542644704800001</v>
+        <v>-2.597934145600001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4203447019028507</v>
+        <v>0.4411527408974535</v>
       </c>
       <c r="T83">
-        <v>4.486949017815796</v>
+        <v>4.736223963250008</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.1082666041361011</v>
+        <v>0.106946279695417</v>
       </c>
       <c r="W83">
-        <v>0.2102707347447074</v>
+        <v>0.2105820672478207</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4009874227263005</v>
+        <v>0.396097332205248</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2520847885047546</v>
+        <v>0.2539847885047546</v>
       </c>
       <c r="C84">
-        <v>3.324477182671263</v>
+        <v>2.980368245421992</v>
       </c>
       <c r="D84">
-        <v>4.262877182671271</v>
+        <v>4.239968245422</v>
       </c>
       <c r="E84">
-        <v>24.31840000000001</v>
+        <v>24.63960000000001</v>
       </c>
       <c r="F84">
-        <v>26.33840000000001</v>
+        <v>26.6596</v>
       </c>
       <c r="G84">
         <v>25.4</v>
@@ -8175,37 +8175,37 @@
         <v>2.46</v>
       </c>
       <c r="M84">
-        <v>6.210594720000002</v>
+        <v>6.286333680000001</v>
       </c>
       <c r="N84">
-        <v>-3.750594720000002</v>
+        <v>-3.826333680000001</v>
       </c>
       <c r="O84">
-        <v>-1.012660574400001</v>
+        <v>-1.0331100936</v>
       </c>
       <c r="P84">
-        <v>-2.737934145600001</v>
+        <v>-2.793223586400001</v>
       </c>
       <c r="Q84">
-        <v>-2.597934145600001</v>
+        <v>-2.653223586400001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4411527408974535</v>
+        <v>0.4644087844796567</v>
       </c>
       <c r="T84">
-        <v>4.736223963250008</v>
+        <v>5.014825372852949</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.106946279695417</v>
+        <v>0.1056577703014963</v>
       </c>
       <c r="W84">
-        <v>0.2105820672478207</v>
+        <v>0.2108858977629072</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.396097332205248</v>
+        <v>0.391325075190727</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2539847885047546</v>
+        <v>0.2558847885047546</v>
       </c>
       <c r="C85">
-        <v>2.980368245421992</v>
+        <v>2.636504219790432</v>
       </c>
       <c r="D85">
-        <v>4.239968245422</v>
+        <v>4.217304219790439</v>
       </c>
       <c r="E85">
-        <v>24.63960000000001</v>
+        <v>24.96080000000001</v>
       </c>
       <c r="F85">
-        <v>26.6596</v>
+        <v>26.98080000000001</v>
       </c>
       <c r="G85">
         <v>25.4</v>
@@ -8257,37 +8257,37 @@
         <v>2.46</v>
       </c>
       <c r="M85">
-        <v>6.286333680000001</v>
+        <v>6.362072640000002</v>
       </c>
       <c r="N85">
-        <v>-3.826333680000001</v>
+        <v>-3.902072640000002</v>
       </c>
       <c r="O85">
-        <v>-1.0331100936</v>
+        <v>-1.053559612800001</v>
       </c>
       <c r="P85">
-        <v>-2.793223586400001</v>
+        <v>-2.848513027200001</v>
       </c>
       <c r="Q85">
-        <v>-2.653223586400001</v>
+        <v>-2.708513027200001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4644087844796567</v>
+        <v>0.4905718335096352</v>
       </c>
       <c r="T85">
-        <v>5.014825372852949</v>
+        <v>5.328251958656259</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.1056577703014963</v>
+        <v>0.1043999397026689</v>
       </c>
       <c r="W85">
-        <v>0.2108858977629072</v>
+        <v>0.2111824942181107</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.391325075190727</v>
+        <v>0.3866664433432183</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2558847885047545</v>
+        <v>0.2577847885047546</v>
       </c>
       <c r="C86">
-        <v>2.636504219790435</v>
+        <v>2.292881199258616</v>
       </c>
       <c r="D86">
-        <v>4.217304219790439</v>
+        <v>4.194881199258621</v>
       </c>
       <c r="E86">
-        <v>24.9608</v>
+        <v>25.282</v>
       </c>
       <c r="F86">
-        <v>26.9808</v>
+        <v>27.302</v>
       </c>
       <c r="G86">
         <v>25.4</v>
@@ -8339,37 +8339,37 @@
         <v>2.46</v>
       </c>
       <c r="M86">
-        <v>6.362072640000001</v>
+        <v>6.437811600000001</v>
       </c>
       <c r="N86">
-        <v>-3.902072640000001</v>
+        <v>-3.977811600000001</v>
       </c>
       <c r="O86">
-        <v>-1.0535596128</v>
+        <v>-1.074009132</v>
       </c>
       <c r="P86">
-        <v>-2.848513027200001</v>
+        <v>-2.903802468</v>
       </c>
       <c r="Q86">
-        <v>-2.7085130272</v>
+        <v>-2.763802468</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.490571833509635</v>
+        <v>0.520223289076944</v>
       </c>
       <c r="T86">
-        <v>5.328251958656256</v>
+        <v>5.683468755900007</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.104399939702669</v>
+        <v>0.1031717051179317</v>
       </c>
       <c r="W86">
-        <v>0.2111824942181107</v>
+        <v>0.2114721119331917</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3866664433432183</v>
+        <v>0.38211742636271</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2577847885047546</v>
+        <v>0.2596847885047546</v>
       </c>
       <c r="C87">
-        <v>2.292881199258616</v>
+        <v>1.949495359951566</v>
       </c>
       <c r="D87">
-        <v>4.194881199258621</v>
+        <v>4.172695359951571</v>
       </c>
       <c r="E87">
-        <v>25.282</v>
+        <v>25.6032</v>
       </c>
       <c r="F87">
-        <v>27.302</v>
+        <v>27.6232</v>
       </c>
       <c r="G87">
         <v>25.4</v>
@@ -8421,37 +8421,37 @@
         <v>2.46</v>
       </c>
       <c r="M87">
-        <v>6.437811600000001</v>
+        <v>6.513550560000001</v>
       </c>
       <c r="N87">
-        <v>-3.977811600000001</v>
+        <v>-4.053550560000001</v>
       </c>
       <c r="O87">
-        <v>-1.074009132</v>
+        <v>-1.094458651200001</v>
       </c>
       <c r="P87">
-        <v>-2.903802468</v>
+        <v>-2.959091908800001</v>
       </c>
       <c r="Q87">
-        <v>-2.763802468</v>
+        <v>-2.819091908800001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.520223289076944</v>
+        <v>0.5541106668681544</v>
       </c>
       <c r="T87">
-        <v>5.683468755900007</v>
+        <v>6.089430809892865</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.1031717051179317</v>
+        <v>0.1019720341281883</v>
       </c>
       <c r="W87">
-        <v>0.2114721119331917</v>
+        <v>0.2117549943525732</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.38211742636271</v>
+        <v>0.3776742004747714</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2596847885047546</v>
+        <v>0.2615847885047546</v>
       </c>
       <c r="C88">
-        <v>1.949495359951566</v>
+        <v>1.606342958463383</v>
       </c>
       <c r="D88">
-        <v>4.172695359951571</v>
+        <v>4.150742958463391</v>
       </c>
       <c r="E88">
-        <v>25.6032</v>
+        <v>25.92440000000001</v>
       </c>
       <c r="F88">
-        <v>27.6232</v>
+        <v>27.94440000000001</v>
       </c>
       <c r="G88">
         <v>25.4</v>
@@ -8503,37 +8503,37 @@
         <v>2.46</v>
       </c>
       <c r="M88">
-        <v>6.513550560000001</v>
+        <v>6.589289520000001</v>
       </c>
       <c r="N88">
-        <v>-4.053550560000001</v>
+        <v>-4.129289520000001</v>
       </c>
       <c r="O88">
-        <v>-1.094458651200001</v>
+        <v>-1.1149081704</v>
       </c>
       <c r="P88">
-        <v>-2.959091908800001</v>
+        <v>-3.014381349600001</v>
       </c>
       <c r="Q88">
-        <v>-2.819091908800001</v>
+        <v>-2.874381349600001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5541106668681544</v>
+        <v>0.5932114873964739</v>
       </c>
       <c r="T88">
-        <v>6.089430809892865</v>
+        <v>6.557848564500008</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.1019720341281883</v>
+        <v>0.1007999417818873</v>
       </c>
       <c r="W88">
-        <v>0.2117549943525732</v>
+        <v>0.212031373727831</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3776742004747714</v>
+        <v>0.3733331177106936</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2615847885047546</v>
+        <v>0.2634847885047546</v>
       </c>
       <c r="C89">
-        <v>1.606342958463383</v>
+        <v>1.263420329751614</v>
       </c>
       <c r="D89">
-        <v>4.150742958463391</v>
+        <v>4.12902032975162</v>
       </c>
       <c r="E89">
-        <v>25.92440000000001</v>
+        <v>26.2456</v>
       </c>
       <c r="F89">
-        <v>27.94440000000001</v>
+        <v>28.2656</v>
       </c>
       <c r="G89">
         <v>25.4</v>
@@ -8585,37 +8585,37 @@
         <v>2.46</v>
       </c>
       <c r="M89">
-        <v>6.589289520000001</v>
+        <v>6.665028480000001</v>
       </c>
       <c r="N89">
-        <v>-4.129289520000001</v>
+        <v>-4.205028480000001</v>
       </c>
       <c r="O89">
-        <v>-1.1149081704</v>
+        <v>-1.1353576896</v>
       </c>
       <c r="P89">
-        <v>-3.014381349600001</v>
+        <v>-3.069670790400001</v>
       </c>
       <c r="Q89">
-        <v>-2.874381349600001</v>
+        <v>-2.929670790400001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5932114873964739</v>
+        <v>0.6388291113461801</v>
       </c>
       <c r="T89">
-        <v>6.557848564500008</v>
+        <v>7.10433594487501</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.1007999417818873</v>
+        <v>0.09965448789800219</v>
       </c>
       <c r="W89">
-        <v>0.212031373727831</v>
+        <v>0.2123014717536511</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3733331177106936</v>
+        <v>0.3690906959185266</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2634847885047546</v>
+        <v>0.2653847885047546</v>
       </c>
       <c r="C90">
-        <v>1.263420329751614</v>
+        <v>0.9207238850973454</v>
       </c>
       <c r="D90">
-        <v>4.12902032975162</v>
+        <v>4.107523885097352</v>
       </c>
       <c r="E90">
-        <v>26.2456</v>
+        <v>26.5668</v>
       </c>
       <c r="F90">
-        <v>28.2656</v>
+        <v>28.5868</v>
       </c>
       <c r="G90">
         <v>25.4</v>
@@ -8667,37 +8667,37 @@
         <v>2.46</v>
       </c>
       <c r="M90">
-        <v>6.665028480000001</v>
+        <v>6.740767440000001</v>
       </c>
       <c r="N90">
-        <v>-4.205028480000001</v>
+        <v>-4.280767440000001</v>
       </c>
       <c r="O90">
-        <v>-1.1353576896</v>
+        <v>-1.1558072088</v>
       </c>
       <c r="P90">
-        <v>-3.069670790400001</v>
+        <v>-3.124960231200001</v>
       </c>
       <c r="Q90">
-        <v>-2.929670790400001</v>
+        <v>-2.984960231200001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6388291113461801</v>
+        <v>0.6927408487412874</v>
       </c>
       <c r="T90">
-        <v>7.10433594487501</v>
+        <v>7.750184667136375</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.09965448789800219</v>
+        <v>0.09853477455083363</v>
       </c>
       <c r="W90">
-        <v>0.2123014717536511</v>
+        <v>0.2125655001609134</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3690906959185266</v>
+        <v>0.3649436094475319</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2653847885047546</v>
+        <v>0.2672847885047546</v>
       </c>
       <c r="C91">
-        <v>0.9207238850973454</v>
+        <v>0.5782501101287529</v>
       </c>
       <c r="D91">
-        <v>4.107523885097352</v>
+        <v>4.086250110128759</v>
       </c>
       <c r="E91">
-        <v>26.5668</v>
+        <v>26.88800000000001</v>
       </c>
       <c r="F91">
-        <v>28.5868</v>
+        <v>28.908</v>
       </c>
       <c r="G91">
         <v>25.4</v>
@@ -8749,37 +8749,37 @@
         <v>2.46</v>
       </c>
       <c r="M91">
-        <v>6.740767440000001</v>
+        <v>6.816506400000002</v>
       </c>
       <c r="N91">
-        <v>-4.280767440000001</v>
+        <v>-4.356506400000002</v>
       </c>
       <c r="O91">
-        <v>-1.1558072088</v>
+        <v>-1.176256728</v>
       </c>
       <c r="P91">
-        <v>-3.124960231200001</v>
+        <v>-3.180249672000001</v>
       </c>
       <c r="Q91">
-        <v>-2.984960231200001</v>
+        <v>-3.040249672000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6927408487412874</v>
+        <v>0.7574349336154163</v>
       </c>
       <c r="T91">
-        <v>7.750184667136375</v>
+        <v>8.525203133850013</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.09853477455083363</v>
+        <v>0.09743994372249103</v>
       </c>
       <c r="W91">
-        <v>0.2125655001609134</v>
+        <v>0.2128236612702366</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3649436094475319</v>
+        <v>0.3608886804536704</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2672847885047546</v>
+        <v>0.2691847885047546</v>
       </c>
       <c r="C92">
-        <v>0.5782501101287529</v>
+        <v>0.2359955629057033</v>
       </c>
       <c r="D92">
-        <v>4.086250110128759</v>
+        <v>4.065195562905711</v>
       </c>
       <c r="E92">
-        <v>26.88800000000001</v>
+        <v>27.20920000000001</v>
       </c>
       <c r="F92">
-        <v>28.908</v>
+        <v>29.22920000000001</v>
       </c>
       <c r="G92">
         <v>25.4</v>
@@ -8831,37 +8831,37 @@
         <v>2.46</v>
       </c>
       <c r="M92">
-        <v>6.816506400000002</v>
+        <v>6.892245360000001</v>
       </c>
       <c r="N92">
-        <v>-4.356506400000002</v>
+        <v>-4.432245360000001</v>
       </c>
       <c r="O92">
-        <v>-1.176256728</v>
+        <v>-1.196706247200001</v>
       </c>
       <c r="P92">
-        <v>-3.180249672000001</v>
+        <v>-3.235539112800001</v>
       </c>
       <c r="Q92">
-        <v>-3.040249672000001</v>
+        <v>-3.0955391128</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7574349336154163</v>
+        <v>0.836505481794907</v>
       </c>
       <c r="T92">
-        <v>8.525203133850013</v>
+        <v>9.472447926500015</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.09743994372249103</v>
+        <v>0.09636917511015596</v>
       </c>
       <c r="W92">
-        <v>0.2128236612702366</v>
+        <v>0.2130761485090252</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3608886804536704</v>
+        <v>0.3569228707783554</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2691847885047546</v>
+        <v>0.2710847885047546</v>
       </c>
       <c r="C93">
-        <v>0.2359955629057033</v>
+        <v>-0.1060431279367009</v>
       </c>
       <c r="D93">
-        <v>4.065195562905711</v>
+        <v>4.044356872063307</v>
       </c>
       <c r="E93">
-        <v>27.20920000000001</v>
+        <v>27.53040000000001</v>
       </c>
       <c r="F93">
-        <v>29.22920000000001</v>
+        <v>29.55040000000001</v>
       </c>
       <c r="G93">
         <v>25.4</v>
@@ -8913,37 +8913,37 @@
         <v>2.46</v>
       </c>
       <c r="M93">
-        <v>6.892245360000001</v>
+        <v>6.967984320000002</v>
       </c>
       <c r="N93">
-        <v>-4.432245360000001</v>
+        <v>-4.507984320000002</v>
       </c>
       <c r="O93">
-        <v>-1.196706247200001</v>
+        <v>-1.217155766400001</v>
       </c>
       <c r="P93">
-        <v>-3.235539112800001</v>
+        <v>-3.290828553600002</v>
       </c>
       <c r="Q93">
-        <v>-3.0955391128</v>
+        <v>-3.150828553600002</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.836505481794907</v>
+        <v>0.9353436670192704</v>
       </c>
       <c r="T93">
-        <v>9.472447926500015</v>
+        <v>10.65650391731252</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.09636917511015596</v>
+        <v>0.09532168407634992</v>
       </c>
       <c r="W93">
-        <v>0.2130761485090252</v>
+        <v>0.2133231468947967</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3569228707783554</v>
+        <v>0.3530432743568515</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2710847885047546</v>
+        <v>0.2729847885047545</v>
       </c>
       <c r="C94">
-        <v>-0.1060431279367009</v>
+        <v>-0.4478692649877942</v>
       </c>
       <c r="D94">
-        <v>4.044356872063307</v>
+        <v>4.023730735012211</v>
       </c>
       <c r="E94">
-        <v>27.53040000000001</v>
+        <v>27.8516</v>
       </c>
       <c r="F94">
-        <v>29.55040000000001</v>
+        <v>29.8716</v>
       </c>
       <c r="G94">
         <v>25.4</v>
@@ -8995,37 +8995,37 @@
         <v>2.46</v>
       </c>
       <c r="M94">
-        <v>6.967984320000002</v>
+        <v>7.043723280000001</v>
       </c>
       <c r="N94">
-        <v>-4.507984320000002</v>
+        <v>-4.583723280000001</v>
       </c>
       <c r="O94">
-        <v>-1.217155766400001</v>
+        <v>-1.2376052856</v>
       </c>
       <c r="P94">
-        <v>-3.290828553600002</v>
+        <v>-3.346117994400001</v>
       </c>
       <c r="Q94">
-        <v>-3.150828553600002</v>
+        <v>-3.2061179944</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.9353436670192704</v>
+        <v>1.062421333736309</v>
       </c>
       <c r="T94">
-        <v>10.65650391731252</v>
+        <v>12.17886161978574</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.09532168407634992</v>
+        <v>0.09429671973144294</v>
       </c>
       <c r="W94">
-        <v>0.2133231468947967</v>
+        <v>0.2135648334873258</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3530432743568515</v>
+        <v>0.3492471101164553</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2729847885047545</v>
+        <v>0.2748847885047546</v>
       </c>
       <c r="C95">
-        <v>-0.4478692649877942</v>
+        <v>-0.7894860838062243</v>
       </c>
       <c r="D95">
-        <v>4.023730735012211</v>
+        <v>4.003313916193784</v>
       </c>
       <c r="E95">
-        <v>27.8516</v>
+        <v>28.17280000000001</v>
       </c>
       <c r="F95">
-        <v>29.8716</v>
+        <v>30.19280000000001</v>
       </c>
       <c r="G95">
         <v>25.4</v>
@@ -9077,37 +9077,37 @@
         <v>2.46</v>
       </c>
       <c r="M95">
-        <v>7.043723280000001</v>
+        <v>7.119462240000002</v>
       </c>
       <c r="N95">
-        <v>-4.583723280000001</v>
+        <v>-4.659462240000002</v>
       </c>
       <c r="O95">
-        <v>-1.2376052856</v>
+        <v>-1.2580548048</v>
       </c>
       <c r="P95">
-        <v>-3.346117994400001</v>
+        <v>-3.401407435200001</v>
       </c>
       <c r="Q95">
-        <v>-3.2061179944</v>
+        <v>-3.261407435200001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.062421333736309</v>
+        <v>1.231858222692361</v>
       </c>
       <c r="T95">
-        <v>12.17886161978574</v>
+        <v>14.20867188975003</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.09429671973144294</v>
+        <v>0.09329356313855523</v>
       </c>
       <c r="W95">
-        <v>0.2135648334873258</v>
+        <v>0.2138013778119287</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3492471101164553</v>
+        <v>0.3455317153279823</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2748847885047546</v>
+        <v>0.2767847885047546</v>
       </c>
       <c r="C96">
-        <v>-0.7894860838062243</v>
+        <v>-1.130896754611939</v>
       </c>
       <c r="D96">
-        <v>4.003313916193784</v>
+        <v>3.983103245388067</v>
       </c>
       <c r="E96">
-        <v>28.17280000000001</v>
+        <v>28.49400000000001</v>
       </c>
       <c r="F96">
-        <v>30.19280000000001</v>
+        <v>30.51400000000001</v>
       </c>
       <c r="G96">
         <v>25.4</v>
@@ -9159,37 +9159,37 @@
         <v>2.46</v>
       </c>
       <c r="M96">
-        <v>7.119462240000002</v>
+        <v>7.195201200000001</v>
       </c>
       <c r="N96">
-        <v>-4.659462240000002</v>
+        <v>-4.735201200000001</v>
       </c>
       <c r="O96">
-        <v>-1.2580548048</v>
+        <v>-1.278504324</v>
       </c>
       <c r="P96">
-        <v>-3.401407435200001</v>
+        <v>-3.456696876000001</v>
       </c>
       <c r="Q96">
-        <v>-3.261407435200001</v>
+        <v>-3.316696876000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.231858222692361</v>
+        <v>1.469069867230834</v>
       </c>
       <c r="T96">
-        <v>14.20867188975003</v>
+        <v>17.05040626770004</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.09329356313855523</v>
+        <v>0.0923115256318336</v>
       </c>
       <c r="W96">
-        <v>0.2138013778119287</v>
+        <v>0.2140329422560136</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3455317153279823</v>
+        <v>0.3418945393771615</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2767847885047546</v>
+        <v>0.2786847885047546</v>
       </c>
       <c r="C97">
-        <v>-1.130896754611939</v>
+        <v>-1.472104383927249</v>
       </c>
       <c r="D97">
-        <v>3.983103245388067</v>
+        <v>3.963095616072759</v>
       </c>
       <c r="E97">
-        <v>28.49400000000001</v>
+        <v>28.81520000000001</v>
       </c>
       <c r="F97">
-        <v>30.51400000000001</v>
+        <v>30.83520000000001</v>
       </c>
       <c r="G97">
         <v>25.4</v>
@@ -9241,37 +9241,37 @@
         <v>2.46</v>
       </c>
       <c r="M97">
-        <v>7.195201200000001</v>
+        <v>7.270940160000002</v>
       </c>
       <c r="N97">
-        <v>-4.735201200000001</v>
+        <v>-4.810940160000002</v>
       </c>
       <c r="O97">
-        <v>-1.278504324</v>
+        <v>-1.298953843200001</v>
       </c>
       <c r="P97">
-        <v>-3.456696876000001</v>
+        <v>-3.511986316800002</v>
       </c>
       <c r="Q97">
-        <v>-3.316696876000001</v>
+        <v>-3.371986316800001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.469069867230834</v>
+        <v>1.824887334038543</v>
       </c>
       <c r="T97">
-        <v>17.05040626770004</v>
+        <v>21.31300783462506</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.0923115256318336</v>
+        <v>0.09134994723983532</v>
       </c>
       <c r="W97">
-        <v>0.2140329422560136</v>
+        <v>0.2142596824408468</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3418945393771615</v>
+        <v>0.3383331379253161</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2786847885047546</v>
+        <v>0.2805847885047545</v>
       </c>
       <c r="C98">
-        <v>-1.472104383927245</v>
+        <v>-1.813112016168606</v>
       </c>
       <c r="D98">
-        <v>3.963095616072759</v>
+        <v>3.943287983831401</v>
       </c>
       <c r="E98">
-        <v>28.8152</v>
+        <v>29.13640000000001</v>
       </c>
       <c r="F98">
-        <v>30.8352</v>
+        <v>31.1564</v>
       </c>
       <c r="G98">
         <v>25.4</v>
@@ -9323,37 +9323,37 @@
         <v>2.46</v>
       </c>
       <c r="M98">
-        <v>7.270940160000001</v>
+        <v>7.346679120000002</v>
       </c>
       <c r="N98">
-        <v>-4.810940160000001</v>
+        <v>-4.886679120000002</v>
       </c>
       <c r="O98">
-        <v>-1.298953843200001</v>
+        <v>-1.319403362400001</v>
       </c>
       <c r="P98">
-        <v>-3.511986316800001</v>
+        <v>-3.567275757600001</v>
       </c>
       <c r="Q98">
-        <v>-3.371986316800001</v>
+        <v>-3.427275757600001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.824887334038539</v>
+        <v>2.417916445384718</v>
       </c>
       <c r="T98">
-        <v>21.31300783462501</v>
+        <v>28.41734377950002</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.09134994723983535</v>
+        <v>0.09040819520643496</v>
       </c>
       <c r="W98">
-        <v>0.2142596824408468</v>
+        <v>0.2144817475703227</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3383331379253161</v>
+        <v>0.3348451674312406</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2805847885047545</v>
+        <v>0.2824847885047546</v>
       </c>
       <c r="C99">
-        <v>-1.813112016168606</v>
+        <v>-2.153922635190938</v>
       </c>
       <c r="D99">
-        <v>3.943287983831401</v>
+        <v>3.923677364809067</v>
       </c>
       <c r="E99">
-        <v>29.13640000000001</v>
+        <v>29.4576</v>
       </c>
       <c r="F99">
-        <v>31.1564</v>
+        <v>31.4776</v>
       </c>
       <c r="G99">
         <v>25.4</v>
@@ -9405,37 +9405,37 @@
         <v>2.46</v>
       </c>
       <c r="M99">
-        <v>7.346679120000002</v>
+        <v>7.422418080000001</v>
       </c>
       <c r="N99">
-        <v>-4.886679120000002</v>
+        <v>-4.962418080000001</v>
       </c>
       <c r="O99">
-        <v>-1.319403362400001</v>
+        <v>-1.3398528816</v>
       </c>
       <c r="P99">
-        <v>-3.567275757600001</v>
+        <v>-3.6225651984</v>
       </c>
       <c r="Q99">
-        <v>-3.427275757600001</v>
+        <v>-3.4825651984</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.417916445384718</v>
+        <v>3.603974668077077</v>
       </c>
       <c r="T99">
-        <v>28.41734377950002</v>
+        <v>42.62601566925002</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.09040819520643496</v>
+        <v>0.08948566260228769</v>
       </c>
       <c r="W99">
-        <v>0.2144817475703227</v>
+        <v>0.2146992807583806</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3348451674312406</v>
+        <v>0.3314283800084729</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2824847885047546</v>
+        <v>0.2843847885047546</v>
       </c>
       <c r="C100">
-        <v>-2.153922635190938</v>
+        <v>-2.494539165786097</v>
       </c>
       <c r="D100">
-        <v>3.923677364809067</v>
+        <v>3.904260834213908</v>
       </c>
       <c r="E100">
-        <v>29.4576</v>
+        <v>29.7788</v>
       </c>
       <c r="F100">
-        <v>31.4776</v>
+        <v>31.7988</v>
       </c>
       <c r="G100">
         <v>25.4</v>
@@ -9487,37 +9487,37 @@
         <v>2.46</v>
       </c>
       <c r="M100">
-        <v>7.422418080000001</v>
+        <v>7.498157040000001</v>
       </c>
       <c r="N100">
-        <v>-4.962418080000001</v>
+        <v>-5.038157040000002</v>
       </c>
       <c r="O100">
-        <v>-1.3398528816</v>
+        <v>-1.3603024008</v>
       </c>
       <c r="P100">
-        <v>-3.6225651984</v>
+        <v>-3.677854639200001</v>
       </c>
       <c r="Q100">
-        <v>-3.4825651984</v>
+        <v>-3.537854639200001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.603974668077077</v>
+        <v>7.162149336154155</v>
       </c>
       <c r="T100">
-        <v>42.62601566925002</v>
+        <v>85.25203133850003</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.08948566260228769</v>
+        <v>0.08858176702044639</v>
       </c>
       <c r="W100">
-        <v>0.2146992807583806</v>
+        <v>0.2149124193365788</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3314283800084729</v>
+        <v>0.3280806185942459</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2843847885047546</v>
-      </c>
-      <c r="C101">
-        <v>-2.494539165786097</v>
-      </c>
-      <c r="D101">
-        <v>3.904260834213908</v>
-      </c>
-      <c r="E101">
-        <v>29.7788</v>
-      </c>
-      <c r="F101">
-        <v>31.7988</v>
-      </c>
-      <c r="G101">
-        <v>25.4</v>
-      </c>
-      <c r="H101">
-        <v>30.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2.6</v>
-      </c>
-      <c r="K101">
-        <v>0.1400000000000001</v>
-      </c>
-      <c r="L101">
-        <v>2.46</v>
-      </c>
-      <c r="M101">
-        <v>7.498157040000001</v>
-      </c>
-      <c r="N101">
-        <v>-5.038157040000002</v>
-      </c>
-      <c r="O101">
-        <v>-1.3603024008</v>
-      </c>
-      <c r="P101">
-        <v>-3.677854639200001</v>
-      </c>
-      <c r="Q101">
-        <v>-3.537854639200001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>7.162149336154155</v>
-      </c>
-      <c r="T101">
-        <v>85.25203133850003</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.08858176702044639</v>
-      </c>
-      <c r="W101">
-        <v>0.2149124193365788</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3280806185942459</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
